--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E2" t="n">
         <v>17</v>
@@ -608,10 +608,10 @@
         <v>50</v>
       </c>
       <c r="P2" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="R2" t="n">
         <v>-0.1</v>
@@ -626,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -732,75 +732,79 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="n">
-        <v>11.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="H4" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="I4" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="J4" t="n">
-        <v>19.8</v>
+        <v>31.5</v>
       </c>
       <c r="K4" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="L4" t="n">
-        <v>38.2</v>
+        <v>57.8</v>
       </c>
       <c r="M4" t="n">
-        <v>43.7</v>
+        <v>51.3</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>7.9</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P4" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.6</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.5</v>
+        <v>6.5</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.3</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
-        <v>27</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>16.6 (5g)</t>
+        </is>
+      </c>
       <c r="X4" t="n">
-        <v>-6.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -814,75 +818,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7</v>
+        <v>23.3</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2</v>
+        <v>23.4</v>
       </c>
       <c r="G5" t="n">
-        <v>14.3</v>
+        <v>22.4</v>
       </c>
       <c r="H5" t="n">
-        <v>12.6</v>
+        <v>22.4</v>
       </c>
       <c r="I5" t="n">
-        <v>11.9</v>
+        <v>21.1</v>
       </c>
       <c r="J5" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="K5" t="n">
-        <v>31.8</v>
+        <v>33.7</v>
       </c>
       <c r="L5" t="n">
-        <v>56.4</v>
+        <v>52.7</v>
       </c>
       <c r="M5" t="n">
-        <v>52.4</v>
+        <v>47</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P5" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="U5" t="n">
         <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>12.0 (7g)</t>
+          <t>16.5 (4g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -896,55 +900,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E6" t="n">
-        <v>8.300000000000001</v>
+        <v>20.3</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>23.8</v>
       </c>
       <c r="G6" t="n">
-        <v>13.4</v>
+        <v>24.6</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9</v>
+        <v>22.9</v>
       </c>
       <c r="I6" t="n">
-        <v>12.2</v>
+        <v>23.2</v>
       </c>
       <c r="J6" t="n">
-        <v>31.5</v>
+        <v>35.8</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>35.7</v>
       </c>
       <c r="L6" t="n">
-        <v>57.8</v>
+        <v>45.9</v>
       </c>
       <c r="M6" t="n">
-        <v>51.3</v>
+        <v>43.8</v>
       </c>
       <c r="N6" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="O6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3</v>
+        <v>-2.3</v>
       </c>
       <c r="R6" t="n">
-        <v>-1</v>
+        <v>0.6</v>
       </c>
       <c r="S6" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>20</v>
@@ -954,17 +958,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>16.6 (5g)</t>
+          <t>27.2 (6g)</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -974,79 +978,79 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8</v>
+        <v>18.2</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="I7" t="n">
-        <v>8.699999999999999</v>
+        <v>18.8</v>
       </c>
       <c r="J7" t="n">
-        <v>16.8</v>
+        <v>29.2</v>
       </c>
       <c r="K7" t="n">
-        <v>20.7</v>
+        <v>29.1</v>
       </c>
       <c r="L7" t="n">
-        <v>60.7</v>
+        <v>50.9</v>
       </c>
       <c r="M7" t="n">
-        <v>48.7</v>
+        <v>45.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
         <v>60</v>
       </c>
       <c r="P7" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.9</v>
+        <v>-0.6</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>13.2 (6g)</t>
+          <t>10.3 (3g)</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,79 +1060,79 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.5</v>
+        <v>19.5</v>
       </c>
       <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24.6</v>
-      </c>
       <c r="H8" t="n">
-        <v>22.9</v>
+        <v>20.7</v>
       </c>
       <c r="I8" t="n">
-        <v>23.2</v>
+        <v>19.4</v>
       </c>
       <c r="J8" t="n">
-        <v>35.8</v>
+        <v>29.2</v>
       </c>
       <c r="K8" t="n">
-        <v>35.7</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
-        <v>45.9</v>
+        <v>54.9</v>
       </c>
       <c r="M8" t="n">
-        <v>43.8</v>
+        <v>55.2</v>
       </c>
       <c r="N8" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3</v>
+        <v>-0.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>-0.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="U8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="V8" t="n">
         <v>7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>27.2 (6g)</t>
+          <t>29.3 (6g)</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1142,75 +1146,75 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="E9" t="n">
-        <v>23.3</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>23.4</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>22.4</v>
+        <v>8.1</v>
       </c>
       <c r="H9" t="n">
-        <v>22.4</v>
+        <v>10.1</v>
       </c>
       <c r="I9" t="n">
-        <v>21.1</v>
+        <v>10.2</v>
       </c>
       <c r="J9" t="n">
-        <v>32.8</v>
+        <v>24.5</v>
       </c>
       <c r="K9" t="n">
-        <v>33.7</v>
+        <v>24.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52.7</v>
+        <v>39.2</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>43.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>-3</v>
       </c>
       <c r="S9" t="n">
-        <v>5.7</v>
+        <v>-4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9</v>
+        <v>-0</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>16.5 (4g)</t>
+          <t>6.3 (3g)</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1220,79 +1224,75 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>11.3</v>
       </c>
       <c r="F10" t="n">
-        <v>18.2</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>19.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>18.3</v>
+        <v>10.8</v>
       </c>
       <c r="I10" t="n">
-        <v>18.8</v>
+        <v>11.6</v>
       </c>
       <c r="J10" t="n">
-        <v>29.2</v>
+        <v>19.8</v>
       </c>
       <c r="K10" t="n">
-        <v>29.1</v>
+        <v>22.1</v>
       </c>
       <c r="L10" t="n">
-        <v>50.9</v>
+        <v>38.2</v>
       </c>
       <c r="M10" t="n">
-        <v>45.5</v>
+        <v>43.7</v>
       </c>
       <c r="N10" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P10" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6</v>
+        <v>-2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
-        <v>27</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>10.3 (3g)</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-15.8</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1302,79 +1302,79 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>11.5</v>
       </c>
       <c r="E11" t="n">
-        <v>18.7</v>
+        <v>14.7</v>
       </c>
       <c r="F11" t="n">
-        <v>22.2</v>
+        <v>13.2</v>
       </c>
       <c r="G11" t="n">
-        <v>21.6</v>
+        <v>14.3</v>
       </c>
       <c r="H11" t="n">
-        <v>21.2</v>
+        <v>12.6</v>
       </c>
       <c r="I11" t="n">
-        <v>22.3</v>
+        <v>11.9</v>
       </c>
       <c r="J11" t="n">
-        <v>35.4</v>
+        <v>32.2</v>
       </c>
       <c r="K11" t="n">
-        <v>35.1</v>
+        <v>31.8</v>
       </c>
       <c r="L11" t="n">
-        <v>48.6</v>
+        <v>56.4</v>
       </c>
       <c r="M11" t="n">
-        <v>46.2</v>
+        <v>52.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>18.6 (5g)</t>
+          <t>12.0 (7g)</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>-5.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1384,79 +1384,79 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>14.4</v>
+        <v>6.8</v>
       </c>
       <c r="G12" t="n">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="H12" t="n">
-        <v>11.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>12.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>31.5</v>
+        <v>16.8</v>
       </c>
       <c r="K12" t="n">
-        <v>31.1</v>
+        <v>20.7</v>
       </c>
       <c r="L12" t="n">
-        <v>47.5</v>
+        <v>60.7</v>
       </c>
       <c r="M12" t="n">
-        <v>45.6</v>
+        <v>48.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.8</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4</v>
+        <v>-3.9</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>16.9 (7g)</t>
+          <t>13.2 (6g)</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1466,79 +1466,79 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="F13" t="n">
-        <v>18.2</v>
+        <v>22.2</v>
       </c>
       <c r="G13" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
       <c r="H13" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="I13" t="n">
-        <v>19.4</v>
+        <v>22.3</v>
       </c>
       <c r="J13" t="n">
-        <v>29.2</v>
+        <v>35.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>35.1</v>
       </c>
       <c r="L13" t="n">
-        <v>54.9</v>
+        <v>48.6</v>
       </c>
       <c r="M13" t="n">
-        <v>55.2</v>
+        <v>46.2</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P13" t="n">
         <v>53</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R13" t="n">
         <v>-0.1</v>
       </c>
-      <c r="R13" t="n">
-        <v>-1.2</v>
-      </c>
       <c r="S13" t="n">
-        <v>-0.3</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8</v>
+        <v>0.2</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>29.3 (6g)</t>
+          <t>18.6 (5g)</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1552,55 +1552,55 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>14.3</v>
       </c>
       <c r="F14" t="n">
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="H14" t="n">
-        <v>10.1</v>
+        <v>11.8</v>
       </c>
       <c r="I14" t="n">
-        <v>10.2</v>
+        <v>12.7</v>
       </c>
       <c r="J14" t="n">
-        <v>24.5</v>
+        <v>31.5</v>
       </c>
       <c r="K14" t="n">
-        <v>24.5</v>
+        <v>31.1</v>
       </c>
       <c r="L14" t="n">
-        <v>39.2</v>
+        <v>47.5</v>
       </c>
       <c r="M14" t="n">
-        <v>43.7</v>
+        <v>45.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P14" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.7</v>
       </c>
-      <c r="R14" t="n">
-        <v>-3</v>
-      </c>
       <c r="S14" t="n">
-        <v>-4.5</v>
+        <v>1.9</v>
       </c>
       <c r="T14" t="n">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="U14" t="n">
         <v>20</v>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.3 (3g)</t>
+          <t>16.9 (7g)</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1634,75 +1634,75 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>14.7</v>
       </c>
       <c r="F15" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="G15" t="n">
-        <v>13.1</v>
+        <v>21.3</v>
       </c>
       <c r="H15" t="n">
-        <v>13.2</v>
+        <v>23.4</v>
       </c>
       <c r="I15" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="J15" t="n">
-        <v>26.1</v>
+        <v>34.1</v>
       </c>
       <c r="K15" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="L15" t="n">
-        <v>52.8</v>
+        <v>39.7</v>
       </c>
       <c r="M15" t="n">
-        <v>46.5</v>
+        <v>43.8</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>10.7</v>
       </c>
       <c r="O15" t="n">
         <v>40</v>
       </c>
       <c r="P15" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.7</v>
+        <v>0.3</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.2</v>
+        <v>-8.4</v>
       </c>
       <c r="S15" t="n">
-        <v>6.3</v>
+        <v>-4.1</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="U15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V15" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>15.2 (6g)</t>
+          <t>26.7 (3g)</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1712,79 +1712,79 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>9.5</v>
       </c>
       <c r="E16" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="G16" t="n">
-        <v>9.300000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>11.3</v>
       </c>
       <c r="J16" t="n">
-        <v>28.3</v>
+        <v>26.4</v>
       </c>
       <c r="K16" t="n">
-        <v>26.1</v>
+        <v>27.7</v>
       </c>
       <c r="L16" t="n">
-        <v>54.9</v>
+        <v>45.6</v>
       </c>
       <c r="M16" t="n">
-        <v>52.6</v>
+        <v>44.6</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P16" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>-1.2</v>
       </c>
       <c r="U16" t="n">
+        <v>14</v>
+      </c>
+      <c r="V16" t="n">
         <v>18</v>
       </c>
-      <c r="V16" t="n">
-        <v>29</v>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>10.2 (5g)</t>
+          <t>9.2 (6g)</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>-5.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1794,79 +1794,79 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
       <c r="E17" t="n">
-        <v>13.3</v>
+        <v>18.3</v>
       </c>
       <c r="F17" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="G17" t="n">
-        <v>22.2</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>23.2</v>
+        <v>13.8</v>
       </c>
       <c r="I17" t="n">
-        <v>22.7</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>33.9</v>
+        <v>29.7</v>
       </c>
       <c r="K17" t="n">
-        <v>35.3</v>
+        <v>29</v>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>56.4</v>
       </c>
       <c r="M17" t="n">
-        <v>44</v>
+        <v>52.9</v>
       </c>
       <c r="N17" t="n">
-        <v>11.2</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P17" t="n">
         <v>50</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="R17" t="n">
-        <v>-6.9</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4</v>
+        <v>0.7</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
         <v>18</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>26.7 (3g)</t>
+          <t>9.2 (5g)</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1876,79 +1876,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E18" t="n">
         <v>12.3</v>
       </c>
       <c r="F18" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>13.5</v>
+        <v>12.3</v>
       </c>
       <c r="H18" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="I18" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="J18" t="n">
-        <v>27.9</v>
+        <v>30.5</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L18" t="n">
-        <v>46.4</v>
+        <v>41.7</v>
       </c>
       <c r="M18" t="n">
-        <v>44.8</v>
+        <v>41.7</v>
       </c>
       <c r="N18" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.6</v>
       </c>
-      <c r="T18" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>18</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>9.2 (6g)</t>
+          <t>11.7 (6g)</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>10.3</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1958,79 +1958,79 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K19" t="n">
         <v>19</v>
       </c>
-      <c r="F19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>28.9</v>
-      </c>
       <c r="L19" t="n">
-        <v>53.8</v>
+        <v>39.6</v>
       </c>
       <c r="M19" t="n">
-        <v>51.7</v>
+        <v>35.3</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P19" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>-1.8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="U19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V19" t="n">
         <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>9.2 (5g)</t>
+          <t>4.2 (5g)</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2044,55 +2044,55 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="E20" t="n">
-        <v>15.3</v>
+        <v>22.7</v>
       </c>
       <c r="F20" t="n">
-        <v>13.4</v>
+        <v>21.2</v>
       </c>
       <c r="G20" t="n">
-        <v>12.6</v>
+        <v>19.9</v>
       </c>
       <c r="H20" t="n">
-        <v>13.4</v>
+        <v>20.8</v>
       </c>
       <c r="I20" t="n">
-        <v>12.7</v>
+        <v>22.1</v>
       </c>
       <c r="J20" t="n">
-        <v>30.6</v>
+        <v>32.8</v>
       </c>
       <c r="K20" t="n">
-        <v>28.5</v>
+        <v>33.9</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1</v>
+        <v>45.1</v>
       </c>
       <c r="M20" t="n">
-        <v>43.2</v>
+        <v>51.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P20" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1</v>
+        <v>-6.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>-1.1</v>
       </c>
       <c r="U20" t="n">
         <v>4</v>
@@ -2102,17 +2102,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>11.7 (6g)</t>
+          <t>21.2 (5g)</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>-10.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2122,79 +2122,79 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
       <c r="E21" t="n">
-        <v>8.300000000000001</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>10.6</v>
+        <v>21.8</v>
       </c>
       <c r="G21" t="n">
-        <v>10.8</v>
+        <v>23.8</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>22.4</v>
       </c>
       <c r="I21" t="n">
-        <v>8.199999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="J21" t="n">
-        <v>24.8</v>
+        <v>31.3</v>
       </c>
       <c r="K21" t="n">
-        <v>20.7</v>
+        <v>28.5</v>
       </c>
       <c r="L21" t="n">
-        <v>45.9</v>
+        <v>66.7</v>
       </c>
       <c r="M21" t="n">
-        <v>39.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="O21" t="n">
+        <v>60</v>
+      </c>
+      <c r="P21" t="n">
         <v>50</v>
       </c>
-      <c r="P21" t="n">
-        <v>37</v>
-      </c>
       <c r="Q21" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="S21" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="V21" t="n">
         <v>29</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>11.0 (4g)</t>
+          <t>14.7 (6g)</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>5.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2204,79 +2204,79 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>11.4</v>
+        <v>18.2</v>
       </c>
       <c r="G22" t="n">
-        <v>11.1</v>
+        <v>19</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>12.9</v>
       </c>
       <c r="I22" t="n">
-        <v>9.199999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="J22" t="n">
-        <v>18.2</v>
+        <v>35.8</v>
       </c>
       <c r="K22" t="n">
-        <v>15.4</v>
+        <v>24.3</v>
       </c>
       <c r="L22" t="n">
-        <v>63.8</v>
+        <v>45.2</v>
       </c>
       <c r="M22" t="n">
-        <v>62</v>
+        <v>40.2</v>
       </c>
       <c r="N22" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
         <v>60</v>
       </c>
       <c r="P22" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.3</v>
+        <v>-5.9</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>11.5</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V22" t="n">
         <v>29</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.2 (5g)</t>
+          <t>0.7 (3g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>21.9</v>
+        <v>-38.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2286,79 +2286,79 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>21.8</v>
+        <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>23.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>22.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>21.5</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>31.3</v>
+        <v>28.3</v>
       </c>
       <c r="K23" t="n">
-        <v>28.5</v>
+        <v>26.1</v>
       </c>
       <c r="L23" t="n">
-        <v>66.7</v>
+        <v>54.9</v>
       </c>
       <c r="M23" t="n">
-        <v>66.09999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="N23" t="n">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V23" t="n">
         <v>29</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>14.7 (6g)</t>
+          <t>10.2 (5g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-1.6</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2372,75 +2372,75 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E24" t="n">
-        <v>11.7</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>11.8</v>
       </c>
       <c r="H24" t="n">
-        <v>20.1</v>
+        <v>11.3</v>
       </c>
       <c r="I24" t="n">
-        <v>20.9</v>
+        <v>12.3</v>
       </c>
       <c r="J24" t="n">
-        <v>23.7</v>
+        <v>27.1</v>
       </c>
       <c r="K24" t="n">
-        <v>30.9</v>
+        <v>26</v>
       </c>
       <c r="L24" t="n">
-        <v>49.9</v>
+        <v>43.7</v>
       </c>
       <c r="M24" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="N24" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P24" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="R24" t="n">
-        <v>-8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.2</v>
+        <v>1.1</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>26.2 (4g)</t>
+          <t>7.9 (7g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1.5</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2450,79 +2450,79 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>13.1</v>
       </c>
       <c r="H25" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="I25" t="n">
-        <v>11.6</v>
+        <v>12.8</v>
       </c>
       <c r="J25" t="n">
-        <v>35.8</v>
+        <v>26.1</v>
       </c>
       <c r="K25" t="n">
-        <v>24.3</v>
+        <v>28.5</v>
       </c>
       <c r="L25" t="n">
-        <v>45.2</v>
+        <v>52.8</v>
       </c>
       <c r="M25" t="n">
-        <v>40.2</v>
+        <v>46.5</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O25" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P25" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="Q25" t="n">
-        <v>-6.9</v>
+        <v>-1.7</v>
       </c>
       <c r="R25" t="n">
-        <v>6.6</v>
+        <v>-0.2</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="T25" t="n">
-        <v>11.5</v>
+        <v>-2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
         <v>29</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.7 (3g)</t>
+          <t>15.2 (6g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>-38.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2536,55 +2536,55 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>14.4</v>
+        <v>11.4</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="H26" t="n">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="I26" t="n">
-        <v>12.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>27.1</v>
+        <v>18.2</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>15.4</v>
       </c>
       <c r="L26" t="n">
-        <v>43.7</v>
+        <v>63.8</v>
       </c>
       <c r="M26" t="n">
-        <v>46.3</v>
+        <v>62</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P26" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S26" t="n">
         <v>1.8</v>
       </c>
-      <c r="R26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-2.6</v>
-      </c>
       <c r="T26" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>8</v>
@@ -2594,17 +2594,17 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>7.9 (7g)</t>
+          <t>2.2 (5g)</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>-10.2</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2618,75 +2618,75 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.4</v>
+        <v>10.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="H27" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="I27" t="n">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>20.6</v>
+        <v>24.8</v>
       </c>
       <c r="K27" t="n">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="L27" t="n">
-        <v>37.7</v>
+        <v>45.9</v>
       </c>
       <c r="M27" t="n">
-        <v>36.8</v>
+        <v>39.5</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="V27" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>4.2 (5g)</t>
+          <t>11.0 (4g)</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>-1.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2696,73 +2696,73 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
       <c r="E28" t="n">
-        <v>20.7</v>
+        <v>13.7</v>
       </c>
       <c r="F28" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>20.4</v>
       </c>
-      <c r="G28" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I28" t="n">
-        <v>22</v>
-      </c>
       <c r="J28" t="n">
-        <v>33</v>
+        <v>22.5</v>
       </c>
       <c r="K28" t="n">
-        <v>34</v>
+        <v>30.4</v>
       </c>
       <c r="L28" t="n">
-        <v>46.4</v>
+        <v>47.8</v>
       </c>
       <c r="M28" t="n">
-        <v>52.2</v>
+        <v>48.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>8.1</v>
       </c>
       <c r="O28" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P28" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.5</v>
+        <v>10.9</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.6</v>
+        <v>-8.4</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.8</v>
+        <v>-0.3</v>
       </c>
       <c r="T28" t="n">
-        <v>-1</v>
+        <v>-7.9</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="V28" t="n">
         <v>18</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>21.2 (5g)</t>
+          <t>26.2 (4g)</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>-3.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="29">
@@ -2867,52 +2867,52 @@
         <v>19.5</v>
       </c>
       <c r="E30" t="n">
-        <v>16.3</v>
+        <v>21.3</v>
       </c>
       <c r="F30" t="n">
-        <v>16.8</v>
+        <v>18.8</v>
       </c>
       <c r="G30" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="H30" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="I30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="K30" t="n">
-        <v>34.3</v>
+        <v>34</v>
       </c>
       <c r="L30" t="n">
-        <v>47.4</v>
+        <v>48.8</v>
       </c>
       <c r="M30" t="n">
-        <v>46.4</v>
+        <v>46.7</v>
       </c>
       <c r="N30" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P30" t="n">
         <v>50</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="R30" t="n">
-        <v>-4.3</v>
+        <v>-2.2</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="T30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="U30" t="n">
         <v>22</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="31">
@@ -3031,52 +3031,52 @@
         <v>11.5</v>
       </c>
       <c r="E32" t="n">
-        <v>21.3</v>
+        <v>13</v>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="G32" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H32" t="n">
-        <v>11.9</v>
+        <v>10.9</v>
       </c>
       <c r="I32" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
       <c r="K32" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="L32" t="n">
-        <v>46.6</v>
+        <v>43.4</v>
       </c>
       <c r="M32" t="n">
-        <v>46.1</v>
+        <v>44.2</v>
       </c>
       <c r="N32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
         <v>40</v>
       </c>
       <c r="P32" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="S32" t="n">
-        <v>0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="U32" t="n">
         <v>22</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="33">
@@ -3109,52 +3109,52 @@
         <v>25.5</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>24.3</v>
       </c>
       <c r="F33" t="n">
-        <v>20.6</v>
+        <v>22.6</v>
       </c>
       <c r="G33" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="H33" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="I33" t="n">
-        <v>25.2</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
       <c r="K33" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="L33" t="n">
-        <v>45.2</v>
+        <v>44.2</v>
       </c>
       <c r="M33" t="n">
-        <v>44.9</v>
+        <v>45.9</v>
       </c>
       <c r="N33" t="n">
-        <v>10.5</v>
+        <v>11.4</v>
       </c>
       <c r="O33" t="n">
+        <v>60</v>
+      </c>
+      <c r="P33" t="n">
         <v>50</v>
       </c>
-      <c r="P33" t="n">
-        <v>47</v>
-      </c>
       <c r="Q33" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R33" t="n">
-        <v>-4.6</v>
+        <v>-3.4</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="U33" t="n">
         <v>22</v>
@@ -3170,12 +3170,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3184,76 +3184,76 @@
         </is>
       </c>
       <c r="D34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H34" t="n">
         <v>14.5</v>
       </c>
-      <c r="E34" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F34" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G34" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H34" t="n">
-        <v>17.9</v>
-      </c>
       <c r="I34" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J34" t="n">
-        <v>26.5</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>25.7</v>
+        <v>31.5</v>
       </c>
       <c r="L34" t="n">
-        <v>52.6</v>
+        <v>44.4</v>
       </c>
       <c r="M34" t="n">
-        <v>53.6</v>
+        <v>44</v>
       </c>
       <c r="N34" t="n">
-        <v>5.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O34" t="n">
+        <v>60</v>
+      </c>
+      <c r="P34" t="n">
         <v>70</v>
       </c>
-      <c r="P34" t="n">
-        <v>60</v>
-      </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0.8</v>
+        <v>-2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>-36.8</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3262,71 +3262,75 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>18.3</v>
       </c>
       <c r="F35" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5</v>
+        <v>17.3</v>
       </c>
       <c r="H35" t="n">
-        <v>12.2</v>
+        <v>16.8</v>
       </c>
       <c r="I35" t="n">
-        <v>13.2</v>
+        <v>16.5</v>
       </c>
       <c r="J35" t="n">
-        <v>25.4</v>
+        <v>30.5</v>
       </c>
       <c r="K35" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>49.3</v>
       </c>
       <c r="M35" t="n">
-        <v>45.7</v>
+        <v>50.4</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.3</v>
+        <v>-2</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V35" t="n">
-        <v>10</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>16.3 (3g)</t>
+        </is>
+      </c>
       <c r="X35" t="n">
-        <v>-1.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3336,59 +3340,59 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="n">
-        <v>27.3</v>
+        <v>16.7</v>
       </c>
       <c r="F36" t="n">
-        <v>25.4</v>
+        <v>15.2</v>
       </c>
       <c r="G36" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="H36" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="I36" t="n">
-        <v>18.2</v>
+        <v>16.9</v>
       </c>
       <c r="J36" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="K36" t="n">
-        <v>31.7</v>
+        <v>33.6</v>
       </c>
       <c r="L36" t="n">
-        <v>46.8</v>
+        <v>51.5</v>
       </c>
       <c r="M36" t="n">
-        <v>43.6</v>
+        <v>45.2</v>
       </c>
       <c r="N36" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="O36" t="n">
+        <v>80</v>
+      </c>
+      <c r="P36" t="n">
         <v>70</v>
       </c>
-      <c r="P36" t="n">
-        <v>43</v>
-      </c>
       <c r="Q36" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="R36" t="n">
-        <v>7.2</v>
+        <v>-1.7</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U36" t="n">
         <v>8</v>
@@ -3398,13 +3402,13 @@
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>-4.6</v>
+        <v>-25.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3414,59 +3418,59 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
       <c r="E37" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="G37" t="n">
-        <v>14.1</v>
+        <v>25.9</v>
       </c>
       <c r="H37" t="n">
-        <v>14.5</v>
+        <v>27.2</v>
       </c>
       <c r="I37" t="n">
-        <v>14.5</v>
+        <v>25.8</v>
       </c>
       <c r="J37" t="n">
-        <v>29</v>
+        <v>37.1</v>
       </c>
       <c r="K37" t="n">
-        <v>31.5</v>
+        <v>36.6</v>
       </c>
       <c r="L37" t="n">
-        <v>44.4</v>
+        <v>45.4</v>
       </c>
       <c r="M37" t="n">
-        <v>44</v>
+        <v>44.2</v>
       </c>
       <c r="N37" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P37" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="R37" t="n">
-        <v>-3.3</v>
+        <v>-1.6</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="T37" t="n">
-        <v>-2.5</v>
+        <v>0.5</v>
       </c>
       <c r="U37" t="n">
         <v>8</v>
@@ -3476,13 +3480,13 @@
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>-17.8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3492,79 +3496,79 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="E38" t="n">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>13.2</v>
       </c>
       <c r="G38" t="n">
-        <v>12.7</v>
+        <v>15</v>
       </c>
       <c r="H38" t="n">
-        <v>11.8</v>
+        <v>16.9</v>
       </c>
       <c r="I38" t="n">
-        <v>10.9</v>
+        <v>16.3</v>
       </c>
       <c r="J38" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="K38" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="L38" t="n">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="P38" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="R38" t="n">
-        <v>3.1</v>
+        <v>-3.1</v>
       </c>
       <c r="S38" t="n">
-        <v>2.3</v>
+        <v>-1.4</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5</v>
+        <v>-1.3</v>
       </c>
       <c r="U38" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="V38" t="n">
         <v>23</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>10.3 (3g)</t>
+          <t>21.7 (3g)</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>4.5</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3574,79 +3578,75 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
       <c r="E39" t="n">
-        <v>18.3</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>19.6</v>
+        <v>5.6</v>
       </c>
       <c r="G39" t="n">
-        <v>17.3</v>
+        <v>5.8</v>
       </c>
       <c r="H39" t="n">
-        <v>16.8</v>
+        <v>7.2</v>
       </c>
       <c r="I39" t="n">
-        <v>16.5</v>
+        <v>7.9</v>
       </c>
       <c r="J39" t="n">
-        <v>30.5</v>
+        <v>22.1</v>
       </c>
       <c r="K39" t="n">
-        <v>28.6</v>
+        <v>24.6</v>
       </c>
       <c r="L39" t="n">
-        <v>49.3</v>
+        <v>58.3</v>
       </c>
       <c r="M39" t="n">
-        <v>50.4</v>
+        <v>51.6</v>
       </c>
       <c r="N39" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>60</v>
       </c>
       <c r="P39" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="Q39" t="n">
-        <v>-2</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>3.1</v>
+        <v>-2.3</v>
       </c>
       <c r="S39" t="n">
-        <v>-1.1</v>
+        <v>6.7</v>
       </c>
       <c r="T39" t="n">
-        <v>1.9</v>
+        <v>-2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V39" t="n">
-        <v>23</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>16.3 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>11.2</v>
+        <v>-33.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3656,79 +3656,75 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
       <c r="E40" t="n">
-        <v>13.3</v>
+        <v>38.7</v>
       </c>
       <c r="F40" t="n">
-        <v>12.4</v>
+        <v>31.6</v>
       </c>
       <c r="G40" t="n">
-        <v>12.8</v>
+        <v>27.7</v>
       </c>
       <c r="H40" t="n">
-        <v>14.3</v>
+        <v>26.1</v>
       </c>
       <c r="I40" t="n">
-        <v>13.1</v>
+        <v>25.6</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
       </c>
       <c r="K40" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
-        <v>42.7</v>
+        <v>50.9</v>
       </c>
       <c r="M40" t="n">
-        <v>44.7</v>
+        <v>50.6</v>
       </c>
       <c r="N40" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P40" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.4</v>
+        <v>-2.9</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.7</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
-        <v>-2</v>
+        <v>0.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="U40" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V40" t="n">
         <v>23</v>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>19.0 (3g)</t>
-        </is>
-      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
-        <v>12.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3738,75 +3734,79 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>12.5</v>
       </c>
       <c r="E41" t="n">
-        <v>16.7</v>
+        <v>11.3</v>
       </c>
       <c r="F41" t="n">
-        <v>15.2</v>
+        <v>13</v>
       </c>
       <c r="G41" t="n">
-        <v>20.2</v>
+        <v>14.9</v>
       </c>
       <c r="H41" t="n">
-        <v>18.8</v>
+        <v>12.4</v>
       </c>
       <c r="I41" t="n">
-        <v>16.9</v>
+        <v>12.3</v>
       </c>
       <c r="J41" t="n">
-        <v>33.5</v>
+        <v>23.1</v>
       </c>
       <c r="K41" t="n">
-        <v>33.6</v>
+        <v>22.1</v>
       </c>
       <c r="L41" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="M41" t="n">
-        <v>45.2</v>
+        <v>47.8</v>
       </c>
       <c r="N41" t="n">
-        <v>10.2</v>
+        <v>5.3</v>
       </c>
       <c r="O41" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P41" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.4</v>
+        <v>-0.2</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.7</v>
+        <v>0.7</v>
       </c>
       <c r="S41" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V41" t="n">
-        <v>9</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>11.3 (3g)</t>
+        </is>
+      </c>
       <c r="X41" t="n">
-        <v>-25.8</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3820,71 +3820,71 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.5</v>
+        <v>11.5</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
+        <v>14.7</v>
       </c>
       <c r="F42" t="n">
-        <v>24.2</v>
+        <v>14.2</v>
       </c>
       <c r="G42" t="n">
-        <v>25.9</v>
+        <v>14.6</v>
       </c>
       <c r="H42" t="n">
-        <v>27.2</v>
+        <v>13.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25.8</v>
+        <v>13.3</v>
       </c>
       <c r="J42" t="n">
-        <v>37.1</v>
+        <v>23.5</v>
       </c>
       <c r="K42" t="n">
-        <v>36.6</v>
+        <v>23.6</v>
       </c>
       <c r="L42" t="n">
-        <v>45.4</v>
+        <v>59.5</v>
       </c>
       <c r="M42" t="n">
-        <v>44.2</v>
+        <v>57.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P42" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.6</v>
+        <v>0.9</v>
       </c>
       <c r="S42" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V42" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>-2</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3894,79 +3894,75 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="E43" t="n">
-        <v>15.7</v>
+        <v>27.3</v>
       </c>
       <c r="F43" t="n">
-        <v>13.2</v>
+        <v>25.4</v>
       </c>
       <c r="G43" t="n">
-        <v>15</v>
+        <v>22.1</v>
       </c>
       <c r="H43" t="n">
-        <v>16.9</v>
+        <v>18.7</v>
       </c>
       <c r="I43" t="n">
-        <v>16.3</v>
+        <v>18.2</v>
       </c>
       <c r="J43" t="n">
-        <v>27.7</v>
+        <v>33.2</v>
       </c>
       <c r="K43" t="n">
-        <v>29</v>
+        <v>31.7</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>46.8</v>
       </c>
       <c r="M43" t="n">
-        <v>50.4</v>
+        <v>43.6</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="O43" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="P43" t="n">
         <v>43</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>-3.1</v>
+        <v>7.2</v>
       </c>
       <c r="S43" t="n">
-        <v>-1.4</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.3</v>
+        <v>1.5</v>
       </c>
       <c r="U43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V43" t="n">
-        <v>23</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>21.7 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
-        <v>15.1</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3980,71 +3976,75 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>15.3</v>
       </c>
       <c r="F44" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="G44" t="n">
-        <v>5.8</v>
+        <v>12.7</v>
       </c>
       <c r="H44" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
       <c r="I44" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="J44" t="n">
-        <v>22.1</v>
+        <v>27</v>
       </c>
       <c r="K44" t="n">
-        <v>24.6</v>
+        <v>26.4</v>
       </c>
       <c r="L44" t="n">
-        <v>58.3</v>
+        <v>47.3</v>
       </c>
       <c r="M44" t="n">
-        <v>51.6</v>
+        <v>45</v>
       </c>
       <c r="N44" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P44" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>-2.3</v>
+        <v>3.1</v>
       </c>
       <c r="S44" t="n">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="T44" t="n">
-        <v>-2.4</v>
+        <v>0.5</v>
       </c>
       <c r="U44" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="V44" t="n">
-        <v>9</v>
-      </c>
-      <c r="W44" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>10.3 (3g)</t>
+        </is>
+      </c>
       <c r="X44" t="n">
-        <v>-33.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4054,75 +4054,79 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
       <c r="E45" t="n">
-        <v>24.7</v>
+        <v>13.3</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
-        <v>29.4</v>
+        <v>12.8</v>
       </c>
       <c r="H45" t="n">
-        <v>29.5</v>
+        <v>14.3</v>
       </c>
       <c r="I45" t="n">
-        <v>28.4</v>
+        <v>13.1</v>
       </c>
       <c r="J45" t="n">
-        <v>33.2</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>33</v>
+        <v>29.3</v>
       </c>
       <c r="L45" t="n">
-        <v>49.9</v>
+        <v>42.7</v>
       </c>
       <c r="M45" t="n">
-        <v>50.4</v>
+        <v>44.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="O45" t="n">
         <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="S45" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="T45" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="U45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V45" t="n">
-        <v>9</v>
-      </c>
-      <c r="W45" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>19.0 (3g)</t>
+        </is>
+      </c>
       <c r="X45" t="n">
-        <v>-13.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4132,80 +4136,80 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="E46" t="n">
-        <v>38.7</v>
+        <v>24.7</v>
       </c>
       <c r="F46" t="n">
-        <v>31.6</v>
+        <v>27</v>
       </c>
       <c r="G46" t="n">
-        <v>27.7</v>
+        <v>29.4</v>
       </c>
       <c r="H46" t="n">
-        <v>26.1</v>
+        <v>29.5</v>
       </c>
       <c r="I46" t="n">
-        <v>25.6</v>
+        <v>28.4</v>
       </c>
       <c r="J46" t="n">
-        <v>30</v>
+        <v>33.2</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L46" t="n">
-        <v>50.9</v>
+        <v>49.9</v>
       </c>
       <c r="M46" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="N46" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>50</v>
+      </c>
+      <c r="P46" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>18</v>
+      </c>
+      <c r="V46" t="n">
         <v>9</v>
-      </c>
-      <c r="O46" t="n">
-        <v>40</v>
-      </c>
-      <c r="P46" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T46" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>21</v>
-      </c>
-      <c r="V46" t="n">
-        <v>23</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
-        <v>5.9</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4214,153 +4218,157 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="E47" t="n">
-        <v>11.3</v>
+        <v>12.7</v>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="G47" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="H47" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I47" t="n">
-        <v>12.3</v>
+        <v>15.6</v>
       </c>
       <c r="J47" t="n">
-        <v>23.1</v>
+        <v>28.7</v>
       </c>
       <c r="K47" t="n">
-        <v>22.1</v>
+        <v>27.7</v>
       </c>
       <c r="L47" t="n">
-        <v>50.6</v>
+        <v>44.5</v>
       </c>
       <c r="M47" t="n">
-        <v>47.8</v>
+        <v>45</v>
       </c>
       <c r="N47" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="O47" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P47" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="R47" t="n">
-        <v>0.7</v>
+        <v>-2.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.8</v>
+        <v>-0.5</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V47" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>11.3 (3g)</t>
+          <t>12.0 (5g)</t>
         </is>
       </c>
       <c r="X47" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="E48" t="n">
-        <v>14.7</v>
+        <v>5.3</v>
       </c>
       <c r="F48" t="n">
-        <v>14.2</v>
+        <v>5.2</v>
       </c>
       <c r="G48" t="n">
-        <v>14.6</v>
+        <v>5.8</v>
       </c>
       <c r="H48" t="n">
-        <v>13.2</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="n">
-        <v>13.3</v>
+        <v>7.5</v>
       </c>
       <c r="J48" t="n">
-        <v>23.5</v>
+        <v>17.8</v>
       </c>
       <c r="K48" t="n">
-        <v>23.6</v>
+        <v>17.6</v>
       </c>
       <c r="L48" t="n">
-        <v>59.5</v>
+        <v>60.1</v>
       </c>
       <c r="M48" t="n">
-        <v>57.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="P48" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.8</v>
+        <v>-0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9</v>
+        <v>-2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="T48" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="U48" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>23</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>5.5 (4g)</t>
+        </is>
+      </c>
       <c r="X48" t="n">
-        <v>30.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4377,72 +4385,72 @@
         <v>14.5</v>
       </c>
       <c r="E49" t="n">
-        <v>12.7</v>
+        <v>21</v>
       </c>
       <c r="F49" t="n">
-        <v>13.2</v>
+        <v>16.2</v>
       </c>
       <c r="G49" t="n">
-        <v>14.4</v>
+        <v>17.3</v>
       </c>
       <c r="H49" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="I49" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="J49" t="n">
-        <v>28.7</v>
+        <v>31.7</v>
       </c>
       <c r="K49" t="n">
-        <v>27.7</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>44.5</v>
+        <v>55.3</v>
       </c>
       <c r="M49" t="n">
-        <v>45</v>
+        <v>44.1</v>
       </c>
       <c r="N49" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="O49" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P49" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="R49" t="n">
-        <v>-2.4</v>
+        <v>2.9</v>
       </c>
       <c r="S49" t="n">
-        <v>-0.5</v>
+        <v>11.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>-0.3</v>
       </c>
       <c r="U49" t="n">
         <v>20</v>
       </c>
       <c r="V49" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>12.0 (5g)</t>
+          <t>12.7 (7g)</t>
         </is>
       </c>
       <c r="X49" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4452,79 +4460,79 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="E50" t="n">
-        <v>5.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>5.2</v>
+        <v>10.8</v>
       </c>
       <c r="G50" t="n">
-        <v>5.8</v>
+        <v>12.1</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>12.9</v>
       </c>
       <c r="I50" t="n">
-        <v>7.5</v>
+        <v>13.1</v>
       </c>
       <c r="J50" t="n">
-        <v>17.8</v>
+        <v>23.7</v>
       </c>
       <c r="K50" t="n">
-        <v>17.6</v>
+        <v>25.9</v>
       </c>
       <c r="L50" t="n">
-        <v>60.1</v>
+        <v>39.7</v>
       </c>
       <c r="M50" t="n">
-        <v>70.09999999999999</v>
+        <v>43.5</v>
       </c>
       <c r="N50" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="P50" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0</v>
+        <v>1.6</v>
       </c>
       <c r="R50" t="n">
         <v>-2.3</v>
       </c>
       <c r="S50" t="n">
-        <v>-10</v>
+        <v>-3.8</v>
       </c>
       <c r="T50" t="n">
-        <v>0.2</v>
+        <v>-2.2</v>
       </c>
       <c r="U50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V50" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>5.5 (4g)</t>
+          <t>15.0 (5g)</t>
         </is>
       </c>
       <c r="X50" t="n">
-        <v>3.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4534,79 +4542,79 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="n">
-        <v>21</v>
+        <v>4.7</v>
       </c>
       <c r="F51" t="n">
-        <v>16.2</v>
+        <v>6.8</v>
       </c>
       <c r="G51" t="n">
-        <v>17.3</v>
+        <v>12.2</v>
       </c>
       <c r="H51" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="J51" t="n">
-        <v>31.7</v>
+        <v>25.8</v>
       </c>
       <c r="K51" t="n">
-        <v>32</v>
+        <v>26.8</v>
       </c>
       <c r="L51" t="n">
-        <v>55.3</v>
+        <v>50</v>
       </c>
       <c r="M51" t="n">
-        <v>44.1</v>
+        <v>50.3</v>
       </c>
       <c r="N51" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="P51" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Q51" t="n">
-        <v>-2.2</v>
+        <v>0.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.9</v>
+        <v>-6.3</v>
       </c>
       <c r="S51" t="n">
-        <v>11.2</v>
+        <v>-0.3</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="U51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V51" t="n">
         <v>3</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>12.7 (7g)</t>
+          <t>13.2 (6g)</t>
         </is>
       </c>
       <c r="X51" t="n">
-        <v>2.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4620,55 +4628,55 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E52" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="F52" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>12.1</v>
+        <v>9.1</v>
       </c>
       <c r="H52" t="n">
-        <v>12.9</v>
+        <v>7.8</v>
       </c>
       <c r="I52" t="n">
-        <v>13.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>23.7</v>
+        <v>20.7</v>
       </c>
       <c r="K52" t="n">
-        <v>25.9</v>
+        <v>23.9</v>
       </c>
       <c r="L52" t="n">
-        <v>39.7</v>
+        <v>48.7</v>
       </c>
       <c r="M52" t="n">
-        <v>43.5</v>
+        <v>47.5</v>
       </c>
       <c r="N52" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="O52" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P52" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="S52" t="n">
-        <v>-3.8</v>
+        <v>1.2</v>
       </c>
       <c r="T52" t="n">
-        <v>-2.2</v>
+        <v>-3.2</v>
       </c>
       <c r="U52" t="n">
         <v>20</v>
@@ -4678,17 +4686,17 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>8.0 (3g)</t>
         </is>
       </c>
       <c r="X52" t="n">
-        <v>9.800000000000001</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4698,79 +4706,79 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
       <c r="E53" t="n">
-        <v>4.7</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>6.8</v>
+        <v>31.2</v>
       </c>
       <c r="G53" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J53" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K53" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="N53" t="n">
         <v>12.2</v>
       </c>
-      <c r="H53" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I53" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K53" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L53" t="n">
-        <v>50</v>
-      </c>
-      <c r="M53" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="N53" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="O53" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P53" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R53" t="n">
-        <v>-6.3</v>
+        <v>6.4</v>
       </c>
       <c r="S53" t="n">
-        <v>-0.3</v>
+        <v>3.5</v>
       </c>
       <c r="T53" t="n">
-        <v>-1.1</v>
+        <v>2.2</v>
       </c>
       <c r="U53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V53" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>13.2 (6g)</t>
+          <t>25.0 (7g)</t>
         </is>
       </c>
       <c r="X53" t="n">
-        <v>9.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4784,55 +4792,55 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="E54" t="n">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="F54" t="n">
-        <v>8.800000000000001</v>
+        <v>13.8</v>
       </c>
       <c r="G54" t="n">
-        <v>9.1</v>
+        <v>15.6</v>
       </c>
       <c r="H54" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="I54" t="n">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J54" t="n">
-        <v>20.7</v>
+        <v>31.1</v>
       </c>
       <c r="K54" t="n">
-        <v>23.9</v>
+        <v>32.8</v>
       </c>
       <c r="L54" t="n">
-        <v>48.7</v>
+        <v>58</v>
       </c>
       <c r="M54" t="n">
-        <v>47.5</v>
+        <v>51.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P54" t="n">
         <v>50</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>1.2</v>
+        <v>6.9</v>
       </c>
       <c r="T54" t="n">
-        <v>-3.2</v>
+        <v>-1.6</v>
       </c>
       <c r="U54" t="n">
         <v>20</v>
@@ -4842,17 +4850,17 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>8.0 (3g)</t>
+          <t>15.1 (7g)</t>
         </is>
       </c>
       <c r="X54" t="n">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4866,75 +4874,75 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>16.7</v>
       </c>
       <c r="F55" t="n">
-        <v>31.2</v>
+        <v>16.4</v>
       </c>
       <c r="G55" t="n">
-        <v>26.1</v>
+        <v>14.4</v>
       </c>
       <c r="H55" t="n">
-        <v>25.4</v>
+        <v>14.3</v>
       </c>
       <c r="I55" t="n">
-        <v>24.8</v>
+        <v>13.8</v>
       </c>
       <c r="J55" t="n">
-        <v>37.4</v>
+        <v>24.1</v>
       </c>
       <c r="K55" t="n">
-        <v>35.2</v>
+        <v>23.7</v>
       </c>
       <c r="L55" t="n">
-        <v>50.2</v>
+        <v>43.4</v>
       </c>
       <c r="M55" t="n">
-        <v>46.7</v>
+        <v>41.3</v>
       </c>
       <c r="N55" t="n">
-        <v>12.2</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
         <v>40</v>
       </c>
       <c r="P55" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="R55" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="S55" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="T55" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V55" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>25.0 (7g)</t>
+          <t>10.6 (5g)</t>
         </is>
       </c>
       <c r="X55" t="n">
-        <v>7</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4944,59 +4952,59 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>12.5</v>
       </c>
       <c r="E56" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F56" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G56" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H56" t="n">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="I56" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="J56" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="K56" t="n">
-        <v>32.8</v>
+        <v>30.7</v>
       </c>
       <c r="L56" t="n">
-        <v>58</v>
+        <v>51.9</v>
       </c>
       <c r="M56" t="n">
-        <v>51.1</v>
+        <v>47.5</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O56" t="n">
         <v>60</v>
       </c>
       <c r="P56" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R56" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="S56" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="T56" t="n">
-        <v>-1.6</v>
+        <v>-1</v>
       </c>
       <c r="U56" t="n">
         <v>20</v>
@@ -5006,17 +5014,17 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>15.1 (7g)</t>
+          <t>16.2 (5g)</t>
         </is>
       </c>
       <c r="X56" t="n">
-        <v>8.300000000000001</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5026,79 +5034,79 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
       <c r="E57" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="F57" t="n">
-        <v>16.4</v>
+        <v>27.2</v>
       </c>
       <c r="G57" t="n">
-        <v>14.4</v>
+        <v>24</v>
       </c>
       <c r="H57" t="n">
-        <v>14.3</v>
+        <v>25.9</v>
       </c>
       <c r="I57" t="n">
-        <v>13.8</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>24.1</v>
+        <v>36.1</v>
       </c>
       <c r="K57" t="n">
-        <v>23.7</v>
+        <v>35.5</v>
       </c>
       <c r="L57" t="n">
-        <v>43.4</v>
+        <v>56.7</v>
       </c>
       <c r="M57" t="n">
-        <v>41.3</v>
+        <v>55</v>
       </c>
       <c r="N57" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="O57" t="n">
         <v>30</v>
       </c>
       <c r="P57" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="R57" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="S57" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="T57" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="U57" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="V57" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>10.6 (5g)</t>
+          <t>29.2 (6g)</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-7.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5112,75 +5120,75 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>24.7</v>
       </c>
       <c r="F58" t="n">
-        <v>13.2</v>
+        <v>22.4</v>
       </c>
       <c r="G58" t="n">
-        <v>14.3</v>
+        <v>22.8</v>
       </c>
       <c r="H58" t="n">
-        <v>12.6</v>
+        <v>19.5</v>
       </c>
       <c r="I58" t="n">
-        <v>12.7</v>
+        <v>22.2</v>
       </c>
       <c r="J58" t="n">
-        <v>29.7</v>
+        <v>31.8</v>
       </c>
       <c r="K58" t="n">
-        <v>30.7</v>
+        <v>31</v>
       </c>
       <c r="L58" t="n">
-        <v>51.9</v>
+        <v>43.5</v>
       </c>
       <c r="M58" t="n">
-        <v>47.5</v>
+        <v>43.4</v>
       </c>
       <c r="N58" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O58" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P58" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="Q58" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.2</v>
       </c>
-      <c r="R58" t="n">
-        <v>0.5</v>
-      </c>
       <c r="S58" t="n">
-        <v>4.4</v>
+        <v>0.1</v>
       </c>
       <c r="T58" t="n">
-        <v>-1</v>
+        <v>0.7</v>
       </c>
       <c r="U58" t="n">
         <v>20</v>
       </c>
       <c r="V58" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>16.2 (5g)</t>
+          <t>20.9 (7g)</t>
         </is>
       </c>
       <c r="X58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5190,236 +5198,72 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="E59" t="n">
-        <v>26.7</v>
+        <v>22.7</v>
       </c>
       <c r="F59" t="n">
-        <v>27.2</v>
+        <v>20.8</v>
       </c>
       <c r="G59" t="n">
-        <v>24</v>
+        <v>16.2</v>
       </c>
       <c r="H59" t="n">
-        <v>25.9</v>
+        <v>17.6</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>36.1</v>
+        <v>29.9</v>
       </c>
       <c r="K59" t="n">
-        <v>35.5</v>
+        <v>29.3</v>
       </c>
       <c r="L59" t="n">
-        <v>56.7</v>
+        <v>43.1</v>
       </c>
       <c r="M59" t="n">
-        <v>55</v>
+        <v>45.7</v>
       </c>
       <c r="N59" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="O59" t="n">
         <v>30</v>
       </c>
       <c r="P59" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q59" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="S59" t="n">
-        <v>1.7</v>
+        <v>-2.6</v>
       </c>
       <c r="T59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U59" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="V59" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>29.2 (6g)</t>
+          <t>14.5 (4g)</t>
         </is>
       </c>
       <c r="X59" t="n">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Forward</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E60" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H60" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I60" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J60" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K60" t="n">
-        <v>31</v>
-      </c>
-      <c r="L60" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="M60" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="N60" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O60" t="n">
-        <v>30</v>
-      </c>
-      <c r="P60" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U60" t="n">
-        <v>20</v>
-      </c>
-      <c r="V60" t="n">
-        <v>3</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>20.9 (7g)</t>
-        </is>
-      </c>
-      <c r="X60" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E61" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="G61" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="H61" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I61" t="n">
-        <v>17</v>
-      </c>
-      <c r="J61" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="L61" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="N61" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O61" t="n">
-        <v>30</v>
-      </c>
-      <c r="P61" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="R61" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S61" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U61" t="n">
-        <v>11</v>
-      </c>
-      <c r="V61" t="n">
-        <v>3</v>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>14.5 (4g)</t>
-        </is>
-      </c>
-      <c r="X61" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5434,7 +5278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -5524,29 +5368,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.509</v>
+        <v>0.539</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.826</v>
+        <v>2.85</v>
       </c>
       <c r="K2" t="n">
-        <v>1.909</v>
+        <v>1.4</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Okongwu averages 15.6 pts in 7 meetings (+2.1 vs line) — supports the UNDER. H2H avg 1.5 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#27). 6/10 signals agree — Trend, Context, Defense, Pace support the UNDER; Volume, HR L30, HR L10 dissent. Projection model targets 13.2 pts (0.3 pts below line; 50% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.7) — highly predictable output near line — supports the UNDER. H2H avg 1.5 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, Trend, Context, Defense support the UNDER; HR L30, HR L10, H2H dissent. Projection model targets 13.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5416,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.602</v>
+        <v>0.604</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5587,10 +5431,10 @@
         <v>2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="K3" t="n">
-        <v>1.935</v>
+        <v>1.4</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -5601,7 +5445,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5611,7 +5455,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5620,36 +5464,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.588</v>
+        <v>0.555</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7</v>
+        <v>14.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1.877</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>1.855</v>
+        <v>1.357</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.6 pts (L5 vs L30) — supports the UNDER. FG% -5.5% trending (L10 vs L30); Minutes down 2.3 recently (L10=19.8 vs L30=22.1). Opponent is strong defense (#8) at slow pace (#27). 7/10 signals agree — HR L30, HR L10, Trend, Defense support the UNDER; Volume, Context, H2H dissent. Projection model targets 7.7 pts (2.8 pts below line; 58% blended confidence [T2]).</t>
+          <t>Hart averages 16.6 pts in 5 meetings (+4.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#20) at above-average pace (#7). 6/10 signals agree — Context, Defense, H2H, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 14.2 pts (1.7 pts above line; 55% blended confidence [T2]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5659,45 +5503,45 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.519</v>
+        <v>0.574</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>11.1</v>
+        <v>21.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.885</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.847</v>
+        <v>1.345</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Daniels's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. FG% +4.0% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#27). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.1 pts (0.4 pts below line; 51% blended confidence [T3]).</t>
+          <t>Alexander-Walker averages 16.5 pts in 4 meetings (-3.0 vs line) — supports the OVER. H2H avg 4.6 pts below season L30; FG% +5.7% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 21.8 pts (2.3 pts above line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5707,7 +5551,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5716,36 +5560,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.549</v>
+        <v>0.539</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>23.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.833</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.893</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Hart averages 16.6 pts in 5 meetings (+4.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#20) at above-average pace (#7). 6/10 signals agree — Context, Defense, H2H, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 14.0 pts (1.5 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
+          <t>Brunson's L30 of 23.2 pts sits 2.3 below the 25.5 line — marginally supports the UNDER. H2H avg 4.0 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 23.9 pts (1.6 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5755,45 +5599,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.589</v>
+        <v>0.711</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.909</v>
+        <v>1.87</v>
       </c>
       <c r="K7" t="n">
-        <v>1.826</v>
+        <v>1.87</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Risacher averages 13.2 pts in 6 meetings (+7.7 vs line) — supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is strong defense (#8) at slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 8.0 pts (2.5 pts above line; 58% blended confidence [T2]). Risk: minutes trending down (16.8 L10 vs 20.7 L30) — role reduction would suppress counting stats.</t>
+          <t>McCollum averages 10.3 pts in 3 meetings (-7.2 vs line) — marginally supports the UNDER. H2H avg 8.5 pts below season L30; TS% shifts -15.8% in this matchup. Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 4/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.9 pts (8.6 pts below line; 71% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5803,45 +5647,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.513</v>
+        <v>0.621</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.769</v>
+        <v>3.05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.98</v>
+        <v>1.357</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Brunson's L30 of 23.2 pts sits 2.3 below the 25.5 line — marginally supports the UNDER. H2H avg 4.0 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 25.0 pts (0.5 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Towns averages 29.3 pts in 6 meetings (+9.8 vs line) — supports the OVER. H2H avg 9.9 pts above season L30; TS% shifts +3.6% in this matchup. Opponent is below-average defense (#17) at above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Context, Defense support the OVER; Volume, Trend, FG Trend dissent. Projection model targets 23.8 pts (4.3 pts above line; 62% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5851,45 +5695,45 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6</v>
+        <v>0.517</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>21.5</v>
+        <v>8.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.909</v>
+        <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>1.826</v>
+        <v>1.4</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Alexander-Walker's L30 of 21.1 pts sits 2.6 above the 18.5 line — supports the OVER. H2H avg 4.6 pts below season L30; FG% +5.7% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#27). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 21.5 pts (3.0 pts above line; 60% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 3.0 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.9 pts below season L30; FG% -4.5% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.1 pts (0.4 pts below line; 51% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5904,40 +5748,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.702</v>
+        <v>0.606</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.87</v>
+        <v>1.417</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>McCollum averages 10.3 pts in 3 meetings (-7.2 vs line) — marginally supports the UNDER. H2H avg 8.5 pts below season L30; TS% shifts -15.8% in this matchup. Opponent is elite defense (#4) at slow pace (#27). Mixed signals: 4/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.3 pts (8.2 pts below line; 70% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 2.6 pts (L5 vs L30) — supports the UNDER. FG% -5.5% trending (L10 vs L30); Minutes down 2.3 recently (L10=19.8 vs L30=22.1). Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — HR L30, HR L10, Trend, Defense support the UNDER; Volume, Context, H2H dissent. Projection model targets 7.0 pts (3.5 pts below line; 60% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5952,40 +5796,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.619</v>
+        <v>0.522</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>18.2</v>
+        <v>10.9</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.971</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.769</v>
+        <v>1.364</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 18.6 pts in 5 meetings (-3.9 vs line) — supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.7% in this matchup. Opponent is strong defense (#8) at slow pace (#27). 6/10 signals agree — Volume, Trend, Context, Defense support the UNDER; HR L30, HR L10, FG Trend dissent. Projection model targets 18.2 pts (4.3 pts below line; 61% blended confidence [T2]).</t>
+          <t>Daniels's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. FG% +4.0% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.9 pts (0.6 pts below line; 52% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5995,45 +5839,45 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.548</v>
+        <v>0.593</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.909</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>1.826</v>
+        <v>1.333</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Bridges averages 16.9 pts in 7 meetings (+3.4 vs line) — marginally supports the UNDER. H2H avg 4.2 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.0 pts (1.5 pts below line; 54% blended confidence [T3]).</t>
+          <t>Risacher averages 13.2 pts in 6 meetings (+7.7 vs line) — supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 8.2 pts (2.7 pts above line; 59% blended confidence [T2]). Risk: minutes trending down (16.8 L10 vs 20.7 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6043,45 +5887,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.617</v>
+        <v>0.591</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>23.7</v>
+        <v>17.9</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1.926</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>1.82</v>
+        <v>1.357</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Towns averages 29.3 pts in 6 meetings (+9.8 vs line) — supports the OVER. H2H avg 9.9 pts above season L30; TS% shifts +3.6% in this matchup. Opponent is below-average defense (#17) at above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Context, Defense support the OVER; Volume, Trend, FG Trend dissent. Projection model targets 23.7 pts (4.2 pts above line; 61% blended confidence [T2]).</t>
+          <t>Johnson averages 18.6 pts in 5 meetings (-2.9 vs line) — marginally supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.7% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.9 pts (3.6 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6091,45 +5935,45 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.531</v>
+        <v>0.524</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.5</v>
+        <v>12.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.909</v>
+        <v>2.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.826</v>
+        <v>1.408</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.0 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.9 pts below season L30; FG% -4.5% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.5 pts (1.0 pts below line; 53% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>[Low conviction — lean only] Bridges averages 16.9 pts in 7 meetings (+4.4 vs line) — supports the lean OVER. H2H avg 4.2 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). 8/10 signals agree — Volume, Trend, Context, Defense support the OVER; HR L30, HR L10 dissent. Projection model targets 12.3 pts (0.2 pts below line; 52% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6148,36 +5992,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.536</v>
+        <v>0.54</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>12.7</v>
+        <v>20.9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.769</v>
+        <v>1.833</v>
       </c>
       <c r="K15" t="n">
-        <v>1.971</v>
+        <v>1.909</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Harris's L30 average of 12.8 pts vs the 13.5 line — supports the UNDER. H2H avg 2.4 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#29). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend dissent. Projection model targets 12.7 pts (0.8 pts below line; 53% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 8.4 pts (L5 vs L30) — supports the UNDER. H2H avg 3.9 pts above season L30; FG% -4.1% trending (L10 vs L30). Opponent is average defense (#14) at moderate pace (#18). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, H2H dissent. Projection model targets 20.9 pts (1.6 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=10.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6187,7 +6031,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6196,36 +6040,36 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.546</v>
+        <v>0.595</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.758</v>
+        <v>1.909</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, FG Trend dissent. Projection model targets 7.9 pts (1.6 pts below line; 54% blended confidence [T3]).</t>
+          <t>Silva's L30 average of 11.3 pts vs the 9.5 line — marginally supports the OVER. H2H avg 2.1 pts below season L30; TS% shifts +10.5% in this matchup. Opponent is average defense (#14) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 13.0 pts (3.5 pts above line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6235,45 +6079,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.515</v>
+        <v>0.502</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>21.5</v>
+        <v>11.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="K17" t="n">
-        <v>1.926</v>
+        <v>1.769</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Banchero averages 26.7 pts in 3 meetings (+6.2 vs line) — marginally supports the OVER. H2H avg 4.0 pts above season L30. Opponent is average defense (#14) at moderate pace (#18). Mixed signals: 3/10 agree (Volume, Context, H2H); counter-signals: HR L30, HR L10, Trend. Projection model targets 21.5 pts (1.0 pts above line; 51% blended confidence [T3]). Risk: L3 has dropped to 13.3 (9.4 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>[Low conviction — lean only] Jr. averages 9.2 pts in 5 meetings (-2.3 vs line) — marginally supports the lean UNDER. H2H avg 2.8 pts below season L30; FG% +3.5% trending (L10 vs L30). Opponent is elite defense (#5) at moderate pace (#18). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]). Risk: L3 has surged to 18.3 after a 20-pt outing (6.3 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6283,45 +6127,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.615</v>
+        <v>0.706</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>13.3</v>
+        <v>7.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.962</v>
+        <v>1.769</v>
       </c>
       <c r="K18" t="n">
-        <v>1.775</v>
+        <v>1.952</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.0 pts (L5 vs L30) — supports the OVER. H2H avg 2.2 pts below season L30; TS% shifts +10.3% in this matchup. Opponent is average defense (#14) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 13.3 pts (3.8 pts above line; 61% blended confidence [T2]).</t>
+          <t>Suggs averages 11.7 pts in 6 meetings (-2.8 vs line) — supports the UNDER. TS% shifts -9.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#18). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 7.3 pts (7.2 pts below line; 70% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6331,45 +6175,45 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.516</v>
+        <v>0.591</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>1.775</v>
+        <v>2.75</v>
       </c>
       <c r="K19" t="n">
-        <v>1.952</v>
+        <v>1.417</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.3 pts (L5 vs L30) — supports the OVER. H2H avg 2.7 pts below season L30. Opponent is elite defense (#5) at moderate pace (#18). 6/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 12.0 pts (0.5 pts above line; 51% blended confidence [T3]).</t>
+          <t>Carter averages 4.2 pts in 5 meetings (-3.3 vs line) — supports the UNDER. H2H avg 2.8 pts below season L30; FG% +4.3% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#18). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend, Min Trend dissent. Projection model targets 4.6 pts (2.9 pts below line; 59% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6379,45 +6223,45 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8.300000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.855</v>
+        <v>1.909</v>
       </c>
       <c r="K20" t="n">
-        <v>1.877</v>
+        <v>1.833</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Suggs averages 11.7 pts in 6 meetings (-2.8 vs line) — supports the UNDER. TS% shifts -10.2% in this matchup; Minutes up 2.1 recently (L10=30.6 vs L30=28.5). Opponent is elite defense (#4) at moderate pace (#18). 8/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Min Trend dissent. Projection model targets 8.3 pts (6.2 pts below line; 68% blended confidence [T1_PREMIUM]).</t>
+          <t>Bane's L30 of 22.1 pts sits 2.6 above the 19.5 line — marginally supports the OVER. TS% shifts -3.5% in this matchup; FG% -6.5% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#18). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 21.4 pts (1.9 pts above line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6436,36 +6280,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.524</v>
+        <v>0.572</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8.9</v>
+        <v>20.2</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.87</v>
+        <v>1.952</v>
       </c>
       <c r="K21" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.4 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 2.8 pts above season L30; TS% shifts +5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.9 pts (0.6 pts below line; 52% blended confidence [T3]).</t>
+          <t>Duren averages 14.7 pts in 6 meetings (-7.8 vs line) — marginally supports the UNDER. H2H avg 6.8 pts below season L30; Minutes up 2.8 recently (L10=31.3 vs L30=28.5). Opponent is average defense (#11) at slow pace (#29). Mixed signals: 5/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 20.2 pts (2.3 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6484,36 +6328,36 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.569</v>
+        <v>0.758</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>15.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.962</v>
+        <v>1.741</v>
       </c>
       <c r="K22" t="n">
-        <v>1.775</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Reed averages 2.2 pts in 5 meetings (-7.3 vs line) — supports the UNDER. H2H avg 7.0 pts below season L30; TS% shifts +21.9% in this matchup. Opponent is strong defense (#8) at slow pace (#29). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 6.9 pts (2.6 pts below line; 56% blended confidence [T3]).</t>
+          <t>Jenkins averages 0.7 pts in 3 meetings (-16.8 vs line) — marginally supports the UNDER. H2H avg 10.9 pts below season L30; TS% shifts -38.4% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 1.9 pts (15.6 pts below line; 75% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 8-pt outing (9.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6532,36 +6376,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.589</v>
+        <v>0.549</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1.833</v>
       </c>
       <c r="K23" t="n">
-        <v>1.893</v>
+        <v>1.909</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Duren averages 14.7 pts in 6 meetings (-7.8 vs line) — marginally supports the UNDER. H2H avg 6.8 pts below season L30; Minutes up 2.8 recently (L10=31.3 vs L30=28.5). Opponent is average defense (#11) at slow pace (#29). Mixed signals: 5/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 19.5 pts (3.0 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, FG Trend dissent. Projection model targets 7.8 pts (1.7 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6571,7 +6415,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6580,36 +6424,36 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.727</v>
+        <v>0.603</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>19.3</v>
+        <v>6.9</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.826</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Wagner averages 26.2 pts in 4 meetings (+14.7 vs line) — supports the OVER. H2H avg 5.3 pts above season L30; Minutes down 7.2 recently (L10=23.7 vs L30=30.9). Opponent is average defense (#14) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 19.3 pts (7.8 pts above line; 72% blended confidence [T3]). Risk: L3 has dropped to 11.7 (9.2 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Robinson averages 7.9 pts in 7 meetings (-2.6 vs line) — marginally supports the UNDER. H2H avg 4.4 pts below season L30; TS% shifts -10.2% in this matchup. Opponent is strong defense (#8) at slow pace (#29). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 6.9 pts (3.6 pts below line; 60% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6628,36 +6472,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.76</v>
+        <v>0.575</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>12.6</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="K25" t="n">
-        <v>1.943</v>
+        <v>1.909</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Jenkins averages 0.7 pts in 3 meetings (-17.8 vs line) — marginally supports the UNDER. H2H avg 10.9 pts below season L30; TS% shifts -38.4% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 1.5 pts (17.0 pts below line; 76% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 8-pt outing (9.4 above L30) — momentum could push over the under line.</t>
+          <t>Harris's L30 average of 12.8 pts vs the 14.5 line — supports the UNDER. H2H avg 2.4 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#29). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend dissent. Projection model targets 12.6 pts (1.9 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6676,36 +6520,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.598</v>
+        <v>0.57</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.787</v>
+        <v>2.05</v>
       </c>
       <c r="K26" t="n">
-        <v>1.943</v>
+        <v>1.73</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Robinson averages 7.9 pts in 7 meetings (-2.6 vs line) — marginally supports the UNDER. H2H avg 4.4 pts below season L30; TS% shifts -10.2% in this matchup. Opponent is strong defense (#8) at slow pace (#29). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.1 pts (3.4 pts below line; 59% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Reed averages 2.2 pts in 5 meetings (-6.3 vs line) — marginally supports the UNDER. H2H avg 7.0 pts below season L30; TS% shifts +21.9% in this matchup. Opponent is strong defense (#8) at slow pace (#29). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 5.6 pts (2.9 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6720,40 +6564,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.59</v>
+        <v>0.548</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.847</v>
+        <v>1.971</v>
       </c>
       <c r="K27" t="n">
-        <v>1.877</v>
+        <v>1.746</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Carter averages 4.2 pts in 5 meetings (-3.3 vs line) — supports the UNDER. H2H avg 2.5 pts below season L30; Minutes up 2.2 recently (L10=20.6 vs L30=18.4). Opponent is elite defense (#4) at moderate pace (#18). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend, Min Trend dissent. Projection model targets 4.9 pts (2.6 pts below line; 59% blended confidence [T2]).</t>
+          <t>Huerter's L30 of 8.2 pts sits 2.3 below the 10.5 line — marginally supports the UNDER. H2H avg 2.8 pts above season L30; TS% shifts +5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.5 pts (2.0 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6772,29 +6616,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.629</v>
+        <v>0.752</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>22.2</v>
+        <v>18.4</v>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>8.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1.746</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.357</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Bane's L30 of 22.0 pts sits 4.5 above the 17.5 line — marginally supports the OVER. TS% shifts -3.5% in this matchup; FG% -5.8% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#18). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 22.2 pts (4.7 pts above line; 62% blended confidence [T3]).</t>
+          <t>Wagner averages 26.2 pts in 4 meetings (+16.7 vs line) — marginally supports the OVER. H2H avg 5.8 pts above season L30; Minutes down 7.9 recently (L10=22.5 vs L30=30.4). Opponent is average defense (#14) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 18.4 pts (8.9 pts above line; 75% blended confidence [T3]). Risk: L3 has dropped to 13.7 (6.7 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6664,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.547</v>
+        <v>0.537</v>
       </c>
       <c r="F29" t="n">
         <v>4</v>
@@ -6829,20 +6673,20 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.926</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.806</v>
+        <v>1.408</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Mobley averages 23.0 pts in 3 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 4.5 pts above season L30; FG% +4.5% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 21.8 pts (2.3 pts above line; 54% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
+          <t>Mobley averages 23.0 pts in 3 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 4.5 pts above season L30; FG% +4.5% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 21.4 pts (1.9 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -6868,29 +6712,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.535</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>18.3</v>
+        <v>17.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.3 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 2/10 agree (HR L10, Trend); counter-signals: Volume, HR L30, Context. Projection model targets 18.3 pts (1.2 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 2.2 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 1/10 agree (Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.6 pts (1.9 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6760,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.543</v>
+        <v>0.542</v>
       </c>
       <c r="F31" t="n">
         <v>8</v>
@@ -6931,10 +6775,10 @@
         <v>0.2</v>
       </c>
       <c r="J31" t="n">
-        <v>1.826</v>
+        <v>2.7</v>
       </c>
       <c r="K31" t="n">
-        <v>1.909</v>
+        <v>1.435</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -6955,16 +6799,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.507</v>
+        <v>0.536</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -6973,20 +6817,20 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
-        <v>1.826</v>
+        <v>1.87</v>
       </c>
       <c r="K32" t="n">
-        <v>1.909</v>
+        <v>1.855</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending up 4.6 pts (L5 vs L30) — marginally supports the lean OVER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.2 pts (0.3 pts below line; 50% blended confidence [T3_LEAN]). Risk: high variance (σ=9.6) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 4.8 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 9.8 pts (1.7 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=10.0) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -7012,41 +6856,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.535</v>
+        <v>0.536</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1.926</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>1.806</v>
+        <v>1.364</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 4.6 pts (L5 vs L30) — marginally supports the OVER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 27.1 pts (1.6 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=10.5) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 3.4 pts (L5 vs L30) — supports the OVER. Opponent is below-average defense (#22) at above-average pace (#6). 6/10 signals agree — Volume, HR L10, Context, Defense support the OVER; HR L30, Trend, H2H dissent. Projection model targets 27.4 pts (1.9 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=11.4) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7060,41 +6904,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.757</v>
+        <v>0.545</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
-        <v>1.758</v>
+        <v>2.9</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>1.385</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Jackson's L30 of 16.5 pts sits 2.0 above the 14.5 line — marginally supports the UNDER. Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 1/10 agree (FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 5.1 pts (9.4 pts below line; 75% blended confidence [T3]). Risk: L3 has surged to 21.3 after a 28-pt outing (4.8 above L30) — momentum could push over the under line.</t>
+          <t>Jr.'s L30 of 14.5 pts sits 4.0 above the 10.5 line — marginally supports the UNDER. Minutes down 2.5 recently (L10=29.0 vs L30=31.5). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.2 pts (1.3 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=9.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7108,36 +6952,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.593</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>9.699999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K35" t="n">
-        <v>1.82</v>
+        <v>1.385</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=5.0) — highly predictable output near line — marginally supports the UNDER. Opponent is average defense (#12) at above-average pace (#10). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, H2H. Projection model targets 9.7 pts (3.8 pts below line; 59% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the UNDER. TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 16.2 pts (2.3 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7147,7 +6991,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7156,19 +7000,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.554</v>
+        <v>0.741</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>19.3</v>
+        <v>3.8</v>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>1.87</v>
@@ -7178,14 +7022,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. FG% +3.2% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 19.3 pts (1.8 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
+          <t>Edgecombe's L30 of 16.9 pts sits 4.4 above the 12.5 line — marginally supports the UNDER. FG% +6.3% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 3.8 pts (8.7 pts below line; 74% blended confidence [T3]). Risk: high variance (σ=10.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7204,7 +7048,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.544</v>
+        <v>0.532</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -7213,27 +7057,27 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>9.300000000000001</v>
+        <v>24.3</v>
       </c>
       <c r="I37" t="n">
         <v>1.2</v>
       </c>
       <c r="J37" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="K37" t="n">
-        <v>1.935</v>
+        <v>1.4</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 of 14.5 pts sits 4.0 above the 10.5 line — marginally supports the UNDER. Minutes down 2.5 recently (L10=29.0 vs L30=31.5). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.3 pts (1.2 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=9.3) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — marginally supports the UNDER. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 24.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7243,7 +7087,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7252,7 +7096,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.55</v>
+        <v>0.543</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
@@ -7261,27 +7105,27 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>11.6</v>
+        <v>14.1</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
-        <v>1.787</v>
+        <v>2.75</v>
       </c>
       <c r="K38" t="n">
-        <v>1.952</v>
+        <v>1.417</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the OVER. TS% shifts +4.5% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, H2H, Pace dissent. Projection model targets 11.6 pts (1.1 pts above line; 54% blended confidence [T3]).</t>
+          <t>Fox averages 21.7 pts in 3 meetings (+6.2 vs line) — supports the UNDER. H2H avg 5.4 pts above season L30; TS% shifts +15.1% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, H2H dissent. Projection model targets 14.1 pts (1.4 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7300,36 +7144,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.576</v>
+        <v>0.587</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>15.7</v>
+        <v>2.9</v>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
-        <v>1.952</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>1.787</v>
+        <v>1.364</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the UNDER. TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 15.7 pts (2.8 pts below line; 57% blended confidence [T3]).</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 2.5 recently (L10=22.1 vs L30=24.6). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.9 pts (2.6 pts below line; 58% blended confidence [T3]). Risk: 73% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7339,45 +7183,45 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.501</v>
+        <v>0.745</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J40" t="n">
-        <v>1.962</v>
+        <v>2.85</v>
       </c>
       <c r="K40" t="n">
-        <v>1.775</v>
+        <v>1.4</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Vassell averages 19.0 pts in 3 meetings (+5.5 vs line) — marginally supports the lean OVER. H2H avg 5.9 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]).</t>
+          <t>Recent scoring trending up 6.0 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 16.5 pts (12.0 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 38.7 after a 21-pt outing (13.1 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7396,36 +7240,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.73</v>
+        <v>0.548</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>10.9</v>
       </c>
       <c r="I41" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1.746</v>
+        <v>3.05</v>
       </c>
       <c r="K41" t="n">
-        <v>2.01</v>
+        <v>1.357</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Edgecombe's L30 of 16.9 pts sits 4.4 above the 12.5 line — marginally supports the UNDER. FG% +6.3% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.2 pts (8.3 pts below line; 72% blended confidence [T3]). Risk: high variance (σ=10.2) makes the outcome difficult to call with confidence.</t>
+          <t>Johnson's L30 average of 12.3 pts vs the 12.5 line — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.9 pts (1.6 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7435,45 +7279,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.508</v>
+        <v>0.756</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>25.7</v>
+        <v>20.8</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>1.82</v>
+        <v>2.85</v>
       </c>
       <c r="K42" t="n">
-        <v>1.917</v>
+        <v>1.4</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Low scoring variance (σ=4.1) — highly predictable output near line — marginally supports the lean UNDER. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 25.7 pts (0.2 pts above line; 50% blended confidence [T3_LEAN]).</t>
+          <t>Harper's L30 average of 13.3 pts vs the 11.5 line — supports the OVER. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, Min Trend dissent. Projection model targets 20.8 pts (9.3 pts above line; 75% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7483,7 +7327,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7492,7 +7336,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
@@ -7501,27 +7345,27 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>13.4</v>
+        <v>19.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
-        <v>1.787</v>
+        <v>2.85</v>
       </c>
       <c r="K43" t="n">
-        <v>1.952</v>
+        <v>1.4</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Fox averages 21.7 pts in 3 meetings (+6.2 vs line) — supports the UNDER. H2H avg 5.4 pts above season L30; TS% shifts +15.1% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, H2H dissent. Projection model targets 13.4 pts (2.1 pts below line; 55% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. FG% +3.2% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 19.4 pts (1.9 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7531,7 +7375,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7540,36 +7384,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.585</v>
+        <v>0.537</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.9</v>
+        <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
-        <v>1.714</v>
+        <v>3.1</v>
       </c>
       <c r="K44" t="n">
-        <v>2.05</v>
+        <v>1.345</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 2.5 recently (L10=22.1 vs L30=24.6). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.9 pts (2.6 pts below line; 58% blended confidence [T3]). Risk: 73% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the OVER. TS% shifts +4.5% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, H2H, Pace dissent. Projection model targets 11.0 pts (0.5 pts above line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7579,16 +7423,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.745</v>
+        <v>0.503</v>
       </c>
       <c r="F45" t="n">
         <v>4</v>
@@ -7597,27 +7441,27 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>11.6</v>
+        <v>13.6</v>
       </c>
       <c r="I45" t="n">
-        <v>16.9</v>
+        <v>0.1</v>
       </c>
       <c r="J45" t="n">
-        <v>1.935</v>
+        <v>3.1</v>
       </c>
       <c r="K45" t="n">
-        <v>1.806</v>
+        <v>1.345</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Embiid's L30 average of 28.4 pts vs the 28.5 line — marginally supports the UNDER. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 4/10 agree (Volume, Trend, Context); counter-signals: HR L30, HR L10, Defense. Projection model targets 11.6 pts (16.9 pts below line; 74% blended confidence [T3]).</t>
+          <t>[Low conviction — lean only] Vassell averages 19.0 pts in 3 meetings (+5.5 vs line) — marginally supports the lean OVER. H2H avg 5.9 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.6 pts (0.1 pts above line; 50% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7636,41 +7480,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.727</v>
+        <v>0.753</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>19.2</v>
+        <v>13.2</v>
       </c>
       <c r="I46" t="n">
-        <v>9.300000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="J46" t="n">
-        <v>1.901</v>
+        <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>1.833</v>
+        <v>1.385</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 6.0 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 19.2 pts (9.3 pts below line; 72% blended confidence [T3]). Risk: L3 has surged to 38.7 after a 21-pt outing (13.1 above L30) — momentum could push over the under line.</t>
+          <t>Embiid's L30 average of 28.4 pts vs the 27.5 line — marginally supports the UNDER. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.2 pts (14.3 pts below line; 75% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7684,7 +7528,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.546</v>
+        <v>0.609</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -7693,75 +7537,75 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
-        <v>1.909</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>1.826</v>
+        <v>1.364</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Johnson's L30 average of 12.3 pts vs the 12.5 line — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 11.0 pts (1.5 pts below line; 54% blended confidence [T3]).</t>
+          <t>Gordon averages 12.0 pts in 5 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 3.6 pts below season L30. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.1 pts (4.4 pts below line; 60% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="F48" t="n">
         <v>7</v>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>19.7</v>
+        <v>5.7</v>
       </c>
       <c r="I48" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1.769</v>
+        <v>2.65</v>
       </c>
       <c r="K48" t="n">
-        <v>1.971</v>
+        <v>1.455</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 13.3 pts vs the 12.5 line — supports the OVER. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, Min Trend dissent. Projection model targets 19.7 pts (7.2 pts above line; 69% blended confidence [T1_PREMIUM]).</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — supports the UNDER. H2H avg 2.0 pts below season L30; TS% shifts +3.5% in this matchup. Opponent is strong defense (#10) at fast pace (#3). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Pace, Min Trend dissent. Projection model targets 5.7 pts (1.8 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7780,36 +7624,36 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.598</v>
+        <v>0.541</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>10.9</v>
+        <v>12.8</v>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
-        <v>1.758</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>1.98</v>
+        <v>1.364</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Gordon averages 12.0 pts in 5 meetings (-2.5 vs line) — marginally supports the UNDER. H2H avg 3.6 pts below season L30. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 4/10 agree (Trend, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.9 pts (3.6 pts below line; 59% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 2.9 pts (L5 vs L30) — marginally supports the UNDER. FG% +11.2% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.8 pts (1.7 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 11-pt outing (7.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7819,7 +7663,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7828,36 +7672,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>1.943</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
-        <v>1.8</v>
+        <v>1.345</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — supports the UNDER. H2H avg 2.0 pts below season L30; TS% shifts +3.5% in this matchup. Opponent is strong defense (#10) at fast pace (#3). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Pace, Min Trend dissent. Projection model targets 6.0 pts (1.5 pts below line; 56% blended confidence [T3]).</t>
+          <t>Jr. averages 15.0 pts in 5 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +9.8% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 14.5 pts (3.0 pts above line; 57% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7867,7 +7711,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7876,7 +7720,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -7885,27 +7729,27 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>12.6</v>
+        <v>15.8</v>
       </c>
       <c r="I51" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
-        <v>1.893</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>1.833</v>
+        <v>1.364</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Camara averages 12.7 pts in 7 meetings (-2.8 vs line) — marginally supports the UNDER. FG% +11.2% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.6 pts (2.9 pts below line; 55% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 11-pt outing (7.7 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 6.3 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +9.1% in this matchup. Opponent is strong defense (#10) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 15.8 pts (3.3 pts above line; 57% blended confidence [T3]). Risk: L3 has dropped to 4.7 (8.4 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7924,36 +7768,36 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.578</v>
+        <v>0.54</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>14.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J52" t="n">
-        <v>1.855</v>
+        <v>2.8</v>
       </c>
       <c r="K52" t="n">
-        <v>1.877</v>
+        <v>1.408</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Jr. averages 15.0 pts in 5 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +9.8% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 14.6 pts (3.1 pts above line; 57% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.3) — highly predictable output near line — supports the OVER. TS% shifts +13.9% in this matchup; Minutes down 3.2 recently (L10=20.7 vs L30=23.9). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 8.8 pts (1.3 pts above line; 54% blended confidence [T3]). Risk: minutes trending down (20.7 L10 vs 23.9 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7963,45 +7807,45 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.603</v>
+        <v>0.514</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>17.1</v>
+        <v>24.4</v>
       </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>0.1</v>
       </c>
       <c r="J53" t="n">
-        <v>1.826</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>1.909</v>
+        <v>1.357</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 6.3 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +9.1% in this matchup. Opponent is strong defense (#10) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 17.1 pts (4.6 pts above line; 60% blended confidence [T3]). Risk: L3 has dropped to 4.7 (8.4 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>[Low conviction — lean only] Recent scoring trending up 6.4 pts (L5 vs L30) — supports the lean OVER. TS% shifts +7.0% in this matchup; FG% +3.5% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, Trend, Context, Defense support the OVER; HR L30, HR L10, Pace dissent. Projection model targets 24.4 pts (0.1 pts below line; 51% blended confidence [T3_LEAN]). Risk: high variance (σ=12.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8016,40 +7860,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.54</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F54" t="n">
         <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>8.800000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="I54" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
-        <v>1.926</v>
+        <v>1.8</v>
       </c>
       <c r="K54" t="n">
-        <v>1.806</v>
+        <v>1.952</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.3) — highly predictable output near line — supports the OVER. TS% shifts +13.9% in this matchup; Minutes down 3.2 recently (L10=20.7 vs L30=23.9). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 8.8 pts (1.3 pts above line; 54% blended confidence [T3]). Risk: minutes trending down (20.7 L10 vs 23.9 L30) — role reduction would suppress counting stats.</t>
+          <t>Braun averages 15.1 pts in 7 meetings (+3.6 vs line) — supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +8.3% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 12.7 pts (1.2 pts above line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8064,40 +7908,40 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.582</v>
       </c>
       <c r="F55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>22.5</v>
+        <v>11.4</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
-        <v>1.775</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>1.962</v>
+        <v>1.364</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 6.4 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +7.0% in this matchup; FG% +3.5% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 4/10 agree (HR L30, HR L10, Context); counter-signals: Volume, Trend, Defense. Projection model targets 22.5 pts (2.0 pts below line; 55% blended confidence [T3]). Risk: high variance (σ=12.2) makes the outcome difficult to call with confidence.</t>
+          <t>Henderson averages 10.6 pts in 5 meetings (-3.9 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace, FG Trend dissent. Projection model targets 11.4 pts (3.1 pts below line; 58% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8107,7 +7951,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8116,36 +7960,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
-        <v>1.769</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>1.364</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Braun averages 15.1 pts in 7 meetings (+2.6 vs line) — supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +8.3% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). 6/10 signals agree — HR L10, Trend, Context, Defense support the OVER; Volume, HR L30, Pace dissent. Projection model targets 13.5 pts (1.0 pts above line; 54% blended confidence [T3]).</t>
+          <t>Johnson averages 16.2 pts in 5 meetings (+3.7 vs line) — marginally supports the UNDER. H2H avg 3.5 pts above season L30; TS% shifts +4.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 3/10 agree (Context, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.7 pts (0.8 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8160,40 +8004,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.604</v>
+        <v>0.545</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
-        <v>1.917</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>1.82</v>
+        <v>1.364</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Henderson averages 10.6 pts in 5 meetings (-4.9 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace, FG Trend dissent. Projection model targets 12.0 pts (3.5 pts below line; 60% blended confidence [T2]).</t>
+          <t>Jokić's L30 average of 26.0 pts vs the 27.5 line — marginally supports the UNDER. H2H avg 3.2 pts above season L30; TS% shifts +6.2% in this matchup. Opponent is weak defense (#28) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 25.3 pts (2.2 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8212,36 +8056,36 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.526</v>
+        <v>0.579</v>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>12.2</v>
+        <v>23.7</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
-        <v>1.885</v>
+        <v>2.8</v>
       </c>
       <c r="K58" t="n">
-        <v>1.847</v>
+        <v>1.408</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 16.2 pts in 5 meetings (+3.7 vs line) — marginally supports the UNDER. H2H avg 3.5 pts above season L30; TS% shifts +4.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 3/10 agree (Context, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 12.2 pts (0.3 pts below line; 52% blended confidence [T3]).</t>
+          <t>Avdija averages 20.9 pts in 7 meetings (-4.6 vs line) — marginally supports the UNDER. TS% shifts +7.4% in this matchup. Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 23.7 pts (1.8 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8260,125 +8104,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.51</v>
+        <v>0.536</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>26.8</v>
+        <v>16.2</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K59" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Jokić's L30 average of 26.0 pts vs the 27.5 line — marginally supports the UNDER. H2H avg 3.2 pts above season L30; TS% shifts +6.2% in this matchup. Opponent is weak defense (#28) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 26.8 pts (0.7 pts below line; 50% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1.877</v>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Avdija averages 20.9 pts in 7 meetings (-4.6 vs line) — marginally supports the UNDER. TS% shifts +7.4% in this matchup. Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 24.1 pts (1.4 pts below line; 56% blended confidence [T3]).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="F61" t="n">
-        <v>6</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1.775</v>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>Holiday averages 14.5 pts in 4 meetings (-4.0 vs line) — supports the UNDER. H2H avg 2.5 pts below season L30. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, Pace dissent. Projection model targets 15.1 pts (3.4 pts below line; 59% blended confidence [T2]). Risk: L3 has surged to 22.7 after a 22-pt outing (5.7 above L30) — momentum could push over the under line.</t>
+          <t>Holiday averages 14.5 pts in 4 meetings (-3.0 vs line) — supports the UNDER. H2H avg 2.5 pts below season L30. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, Pace dissent. Projection model targets 16.2 pts (1.3 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 22-pt outing (5.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8465,7 +8213,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="3">
@@ -8491,7 +8239,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jonathan Kuminga</t>
+          <t>Josh Hart</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8501,17 +8249,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8521,17 +8269,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Hart</t>
+          <t>Jalen Brunson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8541,17 +8289,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8561,17 +8309,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jalen Brunson</t>
+          <t>Karl-Anthony Towns</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8581,17 +8329,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Landry Shamet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8601,17 +8349,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Jonathan Kuminga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8625,13 +8373,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8645,13 +8393,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mikal Bridges</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8661,17 +8409,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karl-Anthony Towns</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8681,17 +8429,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Landry Shamet</t>
+          <t>Mikal Bridges</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8701,17 +8449,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8725,13 +8473,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Tristan da Silva</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8741,7 +8489,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -8751,7 +8499,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8761,17 +8509,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan da Silva</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8781,17 +8529,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8801,17 +8549,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8821,17 +8569,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8845,13 +8593,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8865,13 +8613,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8885,13 +8633,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8901,17 +8649,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8925,13 +8673,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8945,13 +8693,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8965,13 +8713,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Franz Wagner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8985,7 +8733,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="29">
@@ -9061,7 +8809,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -9091,12 +8839,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GG Jackson</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9105,18 +8853,18 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cedric Coward</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CLE @ MEM</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9125,13 +8873,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9141,17 +8889,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9165,13 +8913,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9181,17 +8929,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9205,13 +8953,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9221,17 +8969,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9251,7 +8999,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9261,17 +9009,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LEAN UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>25.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9281,17 +9029,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9301,17 +9049,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9321,17 +9069,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>28.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9345,18 +9093,18 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9365,33 +9113,33 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>POR @ DEN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9411,7 +9159,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9421,17 +9169,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9441,17 +9189,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9465,13 +9213,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9481,17 +9229,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9505,13 +9253,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9525,13 +9273,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>24.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9541,7 +9289,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -9551,7 +9299,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9565,13 +9313,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9585,13 +9333,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9605,47 +9353,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Deni Avdija</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Jrue Holiday</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>POR @ DEN</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E4" t="n">
         <v>8.300000000000001</v>
@@ -769,13 +769,13 @@
         <v>7.9</v>
       </c>
       <c r="O4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3</v>
+        <v>0.7</v>
       </c>
       <c r="R4" t="n">
         <v>-1</v>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E10" t="n">
         <v>11.3</v>
@@ -1261,13 +1261,13 @@
         <v>5.3</v>
       </c>
       <c r="O10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P10" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>-2.6</v>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
@@ -1749,13 +1749,13 @@
         <v>6.5</v>
       </c>
       <c r="O16" t="n">
+        <v>80</v>
+      </c>
+      <c r="P16" t="n">
         <v>60</v>
       </c>
-      <c r="P16" t="n">
-        <v>53</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>-1.1</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E18" t="n">
         <v>12.3</v>
@@ -1913,13 +1913,13 @@
         <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P18" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.3</v>
@@ -1948,7 +1948,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1962,55 +1962,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="E19" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="H19" t="n">
-        <v>7.5</v>
+        <v>14.4</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="J19" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>31.9</v>
       </c>
       <c r="L19" t="n">
-        <v>39.6</v>
+        <v>37.4</v>
       </c>
       <c r="M19" t="n">
-        <v>35.3</v>
+        <v>43.3</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="O19" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P19" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.5</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.8</v>
+        <v>-9.5</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>-5.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>-3.1</v>
       </c>
       <c r="U19" t="n">
         <v>4</v>
@@ -2020,11 +2020,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.2 (5g)</t>
+          <t>10.5 (4g)</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="20">
@@ -2112,7 +2112,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2122,79 +2122,79 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>21.8</v>
+        <v>11.4</v>
       </c>
       <c r="G21" t="n">
-        <v>23.8</v>
+        <v>11.1</v>
       </c>
       <c r="H21" t="n">
-        <v>22.4</v>
+        <v>8.6</v>
       </c>
       <c r="I21" t="n">
-        <v>21.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>31.3</v>
+        <v>18.2</v>
       </c>
       <c r="K21" t="n">
-        <v>28.5</v>
+        <v>15.4</v>
       </c>
       <c r="L21" t="n">
-        <v>66.7</v>
+        <v>63.8</v>
       </c>
       <c r="M21" t="n">
-        <v>66.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="N21" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="O21" t="n">
         <v>60</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1</v>
+        <v>-0.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="T21" t="n">
         <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V21" t="n">
         <v>29</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>14.7 (6g)</t>
+          <t>2.2 (5g)</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>-1.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2208,55 +2208,55 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>18.2</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>19</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>12.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>11.6</v>
+        <v>8.6</v>
       </c>
       <c r="J22" t="n">
-        <v>35.8</v>
+        <v>28.3</v>
       </c>
       <c r="K22" t="n">
-        <v>24.3</v>
+        <v>26.1</v>
       </c>
       <c r="L22" t="n">
-        <v>45.2</v>
+        <v>54.9</v>
       </c>
       <c r="M22" t="n">
-        <v>40.2</v>
+        <v>52.6</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>27</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.9</v>
+        <v>-1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>6.6</v>
+        <v>-0.6</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="T22" t="n">
-        <v>11.5</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
         <v>18</v>
@@ -2266,17 +2266,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.7 (3g)</t>
+          <t>10.2 (5g)</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>-38.4</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2290,55 +2290,55 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>10.6</v>
       </c>
       <c r="G23" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="H23" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>28.3</v>
+        <v>24.8</v>
       </c>
       <c r="K23" t="n">
-        <v>26.1</v>
+        <v>20.7</v>
       </c>
       <c r="L23" t="n">
-        <v>54.9</v>
+        <v>45.9</v>
       </c>
       <c r="M23" t="n">
-        <v>52.6</v>
+        <v>39.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9</v>
+        <v>-4.3</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.6</v>
+        <v>2.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>18</v>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>10.2 (5g)</t>
+          <t>11.0 (4g)</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>-5.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2368,79 +2368,79 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>14.4</v>
+        <v>18.2</v>
       </c>
       <c r="G24" t="n">
-        <v>11.8</v>
+        <v>19</v>
       </c>
       <c r="H24" t="n">
-        <v>11.3</v>
+        <v>12.9</v>
       </c>
       <c r="I24" t="n">
-        <v>12.3</v>
+        <v>11.6</v>
       </c>
       <c r="J24" t="n">
-        <v>27.1</v>
+        <v>35.8</v>
       </c>
       <c r="K24" t="n">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="L24" t="n">
-        <v>43.7</v>
+        <v>45.2</v>
       </c>
       <c r="M24" t="n">
-        <v>46.3</v>
+        <v>40.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="O24" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P24" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.8</v>
+        <v>-7.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="V24" t="n">
         <v>29</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7.9 (7g)</t>
+          <t>0.7 (3g)</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>-10.2</v>
+        <v>-38.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2450,79 +2450,79 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.5</v>
+        <v>6.5</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>6.3</v>
       </c>
       <c r="F25" t="n">
-        <v>12.6</v>
+        <v>5.2</v>
       </c>
       <c r="G25" t="n">
-        <v>13.1</v>
+        <v>7.4</v>
       </c>
       <c r="H25" t="n">
-        <v>13.2</v>
+        <v>7.5</v>
       </c>
       <c r="I25" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
-        <v>26.1</v>
+        <v>20.8</v>
       </c>
       <c r="K25" t="n">
-        <v>28.5</v>
+        <v>19</v>
       </c>
       <c r="L25" t="n">
-        <v>52.8</v>
+        <v>39.6</v>
       </c>
       <c r="M25" t="n">
-        <v>46.5</v>
+        <v>35.3</v>
       </c>
       <c r="N25" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P25" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.7</v>
+        <v>0.5</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="S25" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.4</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>15.2 (6g)</t>
+          <t>4.2 (5g)</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5.3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2532,84 +2532,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.5</v>
+        <v>21.5</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
-        <v>11.4</v>
+        <v>21.8</v>
       </c>
       <c r="G26" t="n">
-        <v>11.1</v>
+        <v>23.8</v>
       </c>
       <c r="H26" t="n">
-        <v>8.6</v>
+        <v>22.4</v>
       </c>
       <c r="I26" t="n">
-        <v>9.199999999999999</v>
+        <v>21.5</v>
       </c>
       <c r="J26" t="n">
-        <v>18.2</v>
+        <v>31.3</v>
       </c>
       <c r="K26" t="n">
-        <v>15.4</v>
+        <v>28.5</v>
       </c>
       <c r="L26" t="n">
-        <v>63.8</v>
+        <v>66.7</v>
       </c>
       <c r="M26" t="n">
-        <v>62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P26" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="S26" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="T26" t="n">
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V26" t="n">
         <v>29</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2.2 (5g)</t>
+          <t>14.7 (6g)</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>21.9</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2618,157 +2618,153 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="n">
-        <v>8.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="F27" t="n">
-        <v>10.6</v>
+        <v>14.2</v>
       </c>
       <c r="G27" t="n">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8.4</v>
+        <v>12.2</v>
       </c>
       <c r="I27" t="n">
-        <v>8.199999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="J27" t="n">
-        <v>24.8</v>
+        <v>25.4</v>
       </c>
       <c r="K27" t="n">
-        <v>20.7</v>
+        <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>45.9</v>
+        <v>44</v>
       </c>
       <c r="M27" t="n">
-        <v>39.5</v>
+        <v>45.7</v>
       </c>
       <c r="N27" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P27" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.3</v>
+        <v>0.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>6.4</v>
+        <v>-1.7</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="U27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V27" t="n">
-        <v>29</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>11.0 (4g)</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>5.1</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="E28" t="n">
-        <v>13.7</v>
+        <v>7.3</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G28" t="n">
-        <v>15.6</v>
+        <v>11.9</v>
       </c>
       <c r="H28" t="n">
-        <v>19.8</v>
+        <v>12.3</v>
       </c>
       <c r="I28" t="n">
-        <v>20.4</v>
+        <v>12.1</v>
       </c>
       <c r="J28" t="n">
-        <v>22.5</v>
+        <v>28.7</v>
       </c>
       <c r="K28" t="n">
-        <v>30.4</v>
+        <v>26.6</v>
       </c>
       <c r="L28" t="n">
-        <v>47.8</v>
+        <v>40.6</v>
       </c>
       <c r="M28" t="n">
-        <v>48.1</v>
+        <v>43.2</v>
       </c>
       <c r="N28" t="n">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="O28" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="P28" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>10.9</v>
+        <v>-4.4</v>
       </c>
       <c r="R28" t="n">
-        <v>-8.4</v>
+        <v>-0.3</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.3</v>
+        <v>-2.6</v>
       </c>
       <c r="T28" t="n">
-        <v>-7.9</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="V28" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>26.2 (4g)</t>
+          <t>10.0 (3g)</t>
         </is>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2778,79 +2774,75 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="E29" t="n">
-        <v>17.3</v>
+        <v>21.3</v>
       </c>
       <c r="F29" t="n">
-        <v>16.6</v>
+        <v>17.6</v>
       </c>
       <c r="G29" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="H29" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="I29" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="J29" t="n">
-        <v>31.1</v>
+        <v>26.5</v>
       </c>
       <c r="K29" t="n">
-        <v>31.2</v>
+        <v>25.7</v>
       </c>
       <c r="L29" t="n">
-        <v>63.8</v>
+        <v>52.6</v>
       </c>
       <c r="M29" t="n">
-        <v>59.3</v>
+        <v>53.6</v>
       </c>
       <c r="N29" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="O29" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P29" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S29" t="n">
         <v>-1</v>
       </c>
-      <c r="R29" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.5</v>
-      </c>
       <c r="T29" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="U29" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>23.0 (3g)</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
-        <v>-2.9</v>
+        <v>-36.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2864,55 +2856,55 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="E30" t="n">
-        <v>21.3</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>18.8</v>
+        <v>9.4</v>
       </c>
       <c r="G30" t="n">
-        <v>22.1</v>
+        <v>8.9</v>
       </c>
       <c r="H30" t="n">
-        <v>20.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>35.3</v>
+        <v>26.2</v>
       </c>
       <c r="K30" t="n">
-        <v>34</v>
+        <v>24.5</v>
       </c>
       <c r="L30" t="n">
-        <v>48.8</v>
+        <v>54.1</v>
       </c>
       <c r="M30" t="n">
-        <v>46.7</v>
+        <v>50.1</v>
       </c>
       <c r="N30" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.5</v>
+        <v>-5.2</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.2</v>
+        <v>1.1</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="U30" t="n">
         <v>22</v>
@@ -2922,17 +2914,17 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>20.5 (6g)</t>
+          <t>5.4 (5g)</t>
         </is>
       </c>
       <c r="X30" t="n">
-        <v>-2.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2946,55 +2938,55 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
       <c r="E31" t="n">
         <v>17.3</v>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="G31" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="H31" t="n">
         <v>18.6</v>
       </c>
       <c r="I31" t="n">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
       <c r="J31" t="n">
-        <v>26.7</v>
+        <v>31.1</v>
       </c>
       <c r="K31" t="n">
-        <v>28.5</v>
+        <v>31.2</v>
       </c>
       <c r="L31" t="n">
-        <v>70.5</v>
+        <v>63.8</v>
       </c>
       <c r="M31" t="n">
-        <v>66.7</v>
+        <v>59.3</v>
       </c>
       <c r="N31" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="P31" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>-3</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="S31" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="T31" t="n">
-        <v>-1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="U31" t="n">
         <v>23</v>
@@ -3004,17 +2996,17 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>15.0 (3g)</t>
+          <t>23.0 (3g)</t>
         </is>
       </c>
       <c r="X31" t="n">
-        <v>1.2</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3028,55 +3020,55 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="E32" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>15.8</v>
+        <v>7.6</v>
       </c>
       <c r="G32" t="n">
-        <v>13.3</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="n">
-        <v>10.9</v>
+        <v>7.5</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>26.1</v>
+        <v>18.9</v>
       </c>
       <c r="K32" t="n">
-        <v>26</v>
+        <v>21.9</v>
       </c>
       <c r="L32" t="n">
-        <v>43.4</v>
+        <v>35.6</v>
       </c>
       <c r="M32" t="n">
-        <v>44.2</v>
+        <v>36.5</v>
       </c>
       <c r="N32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>10</v>
       </c>
-      <c r="O32" t="n">
-        <v>40</v>
-      </c>
-      <c r="P32" t="n">
-        <v>30</v>
-      </c>
       <c r="Q32" t="n">
-        <v>-0.5</v>
+        <v>-6.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.8</v>
+        <v>-0.6</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1</v>
+        <v>-3</v>
       </c>
       <c r="U32" t="n">
         <v>22</v>
@@ -3084,15 +3076,19 @@
       <c r="V32" t="n">
         <v>6</v>
       </c>
-      <c r="W32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>14.7 (7g)</t>
+        </is>
+      </c>
       <c r="X32" t="n">
-        <v>11.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3102,80 +3098,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="E33" t="n">
-        <v>24.3</v>
+        <v>17.3</v>
       </c>
       <c r="F33" t="n">
-        <v>22.6</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>25.5</v>
+        <v>18.8</v>
       </c>
       <c r="H33" t="n">
-        <v>25.2</v>
+        <v>18.6</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>16.6</v>
       </c>
       <c r="J33" t="n">
-        <v>33.8</v>
+        <v>26.7</v>
       </c>
       <c r="K33" t="n">
-        <v>32.7</v>
+        <v>28.5</v>
       </c>
       <c r="L33" t="n">
-        <v>44.2</v>
+        <v>70.5</v>
       </c>
       <c r="M33" t="n">
-        <v>45.9</v>
+        <v>66.7</v>
       </c>
       <c r="N33" t="n">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.4</v>
+        <v>-0.6</v>
       </c>
       <c r="S33" t="n">
-        <v>-1.7</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>1.1</v>
+        <v>-1.8</v>
       </c>
       <c r="U33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V33" t="n">
         <v>6</v>
       </c>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>15.0 (3g)</t>
+        </is>
+      </c>
       <c r="X33" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3184,71 +3184,71 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
-        <v>11.2</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
       <c r="H34" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="I34" t="n">
-        <v>14.5</v>
+        <v>13.3</v>
       </c>
       <c r="J34" t="n">
-        <v>29</v>
+        <v>23.8</v>
       </c>
       <c r="K34" t="n">
-        <v>31.5</v>
+        <v>23.9</v>
       </c>
       <c r="L34" t="n">
-        <v>44.4</v>
+        <v>53.4</v>
       </c>
       <c r="M34" t="n">
-        <v>44</v>
+        <v>53.5</v>
       </c>
       <c r="N34" t="n">
-        <v>9.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
+        <v>70</v>
+      </c>
+      <c r="P34" t="n">
         <v>60</v>
       </c>
-      <c r="P34" t="n">
-        <v>70</v>
-      </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.3</v>
+        <v>4.7</v>
       </c>
       <c r="S34" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="T34" t="n">
-        <v>-2.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U34" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>-17.8</v>
+        <v>-21.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3258,79 +3258,75 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="E35" t="n">
-        <v>18.3</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>19.6</v>
+        <v>11.2</v>
       </c>
       <c r="G35" t="n">
-        <v>17.3</v>
+        <v>14.1</v>
       </c>
       <c r="H35" t="n">
-        <v>16.8</v>
+        <v>14.5</v>
       </c>
       <c r="I35" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J35" t="n">
-        <v>30.5</v>
+        <v>29</v>
       </c>
       <c r="K35" t="n">
-        <v>28.6</v>
+        <v>31.5</v>
       </c>
       <c r="L35" t="n">
-        <v>49.3</v>
+        <v>44.4</v>
       </c>
       <c r="M35" t="n">
-        <v>50.4</v>
+        <v>44</v>
       </c>
       <c r="N35" t="n">
-        <v>5.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>60</v>
       </c>
       <c r="P35" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.1</v>
+        <v>0.4</v>
       </c>
       <c r="T35" t="n">
-        <v>1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V35" t="n">
-        <v>23</v>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>16.3 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
-        <v>11.2</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3344,71 +3340,75 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="E36" t="n">
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
       <c r="F36" t="n">
-        <v>15.2</v>
+        <v>19.6</v>
       </c>
       <c r="G36" t="n">
-        <v>20.2</v>
+        <v>17.3</v>
       </c>
       <c r="H36" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="I36" t="n">
-        <v>16.9</v>
+        <v>16.5</v>
       </c>
       <c r="J36" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="K36" t="n">
-        <v>33.6</v>
+        <v>28.6</v>
       </c>
       <c r="L36" t="n">
-        <v>51.5</v>
+        <v>49.3</v>
       </c>
       <c r="M36" t="n">
-        <v>45.2</v>
+        <v>50.4</v>
       </c>
       <c r="N36" t="n">
-        <v>10.2</v>
+        <v>5.8</v>
       </c>
       <c r="O36" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P36" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.4</v>
+        <v>-1</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.7</v>
+        <v>3.1</v>
       </c>
       <c r="S36" t="n">
-        <v>6.3</v>
+        <v>-1.1</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.1</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>16.3 (3g)</t>
+        </is>
+      </c>
       <c r="X36" t="n">
-        <v>-25.8</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3422,55 +3422,55 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.5</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>16.7</v>
       </c>
       <c r="F37" t="n">
-        <v>24.2</v>
+        <v>15.2</v>
       </c>
       <c r="G37" t="n">
-        <v>25.9</v>
+        <v>20.2</v>
       </c>
       <c r="H37" t="n">
-        <v>27.2</v>
+        <v>18.8</v>
       </c>
       <c r="I37" t="n">
-        <v>25.8</v>
+        <v>16.9</v>
       </c>
       <c r="J37" t="n">
-        <v>37.1</v>
+        <v>33.5</v>
       </c>
       <c r="K37" t="n">
-        <v>36.6</v>
+        <v>33.6</v>
       </c>
       <c r="L37" t="n">
-        <v>45.4</v>
+        <v>51.5</v>
       </c>
       <c r="M37" t="n">
-        <v>44.2</v>
+        <v>45.2</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>10.2</v>
       </c>
       <c r="O37" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P37" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.3</v>
+        <v>4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U37" t="n">
         <v>8</v>
@@ -3480,13 +3480,13 @@
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>-2</v>
+        <v>-25.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3500,75 +3500,71 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
       <c r="E38" t="n">
-        <v>15.7</v>
+        <v>24</v>
       </c>
       <c r="F38" t="n">
-        <v>13.2</v>
+        <v>24.2</v>
       </c>
       <c r="G38" t="n">
-        <v>15</v>
+        <v>25.9</v>
       </c>
       <c r="H38" t="n">
-        <v>16.9</v>
+        <v>27.2</v>
       </c>
       <c r="I38" t="n">
-        <v>16.3</v>
+        <v>25.8</v>
       </c>
       <c r="J38" t="n">
-        <v>27.7</v>
+        <v>37.1</v>
       </c>
       <c r="K38" t="n">
-        <v>29</v>
+        <v>36.6</v>
       </c>
       <c r="L38" t="n">
-        <v>49</v>
+        <v>45.4</v>
       </c>
       <c r="M38" t="n">
-        <v>50.4</v>
+        <v>44.2</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O38" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P38" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="R38" t="n">
-        <v>-3.1</v>
+        <v>-1.6</v>
       </c>
       <c r="S38" t="n">
-        <v>-1.4</v>
+        <v>1.2</v>
       </c>
       <c r="T38" t="n">
-        <v>-1.3</v>
+        <v>0.5</v>
       </c>
       <c r="U38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>23</v>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>21.7 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>15.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3578,75 +3574,79 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7</v>
+        <v>15.7</v>
       </c>
       <c r="F39" t="n">
-        <v>5.6</v>
+        <v>13.2</v>
       </c>
       <c r="G39" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="H39" t="n">
-        <v>7.2</v>
+        <v>16.9</v>
       </c>
       <c r="I39" t="n">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="J39" t="n">
-        <v>22.1</v>
+        <v>27.7</v>
       </c>
       <c r="K39" t="n">
-        <v>24.6</v>
+        <v>29</v>
       </c>
       <c r="L39" t="n">
-        <v>58.3</v>
+        <v>49</v>
       </c>
       <c r="M39" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P39" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.3</v>
+        <v>-3.1</v>
       </c>
       <c r="S39" t="n">
-        <v>6.7</v>
+        <v>-1.4</v>
       </c>
       <c r="T39" t="n">
-        <v>-2.4</v>
+        <v>-1.3</v>
       </c>
       <c r="U39" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V39" t="n">
-        <v>9</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>21.7 (3g)</t>
+        </is>
+      </c>
       <c r="X39" t="n">
-        <v>-33.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3660,71 +3660,71 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.5</v>
+        <v>5.5</v>
       </c>
       <c r="E40" t="n">
-        <v>38.7</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>31.6</v>
+        <v>5.6</v>
       </c>
       <c r="G40" t="n">
-        <v>27.7</v>
+        <v>5.8</v>
       </c>
       <c r="H40" t="n">
-        <v>26.1</v>
+        <v>7.2</v>
       </c>
       <c r="I40" t="n">
-        <v>25.6</v>
+        <v>7.9</v>
       </c>
       <c r="J40" t="n">
-        <v>30</v>
+        <v>22.1</v>
       </c>
       <c r="K40" t="n">
-        <v>30</v>
+        <v>24.6</v>
       </c>
       <c r="L40" t="n">
-        <v>50.9</v>
+        <v>58.3</v>
       </c>
       <c r="M40" t="n">
-        <v>50.6</v>
+        <v>51.6</v>
       </c>
       <c r="N40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O40" t="n">
+        <v>60</v>
+      </c>
+      <c r="P40" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>8</v>
+      </c>
+      <c r="V40" t="n">
         <v>9</v>
-      </c>
-      <c r="O40" t="n">
-        <v>40</v>
-      </c>
-      <c r="P40" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="R40" t="n">
-        <v>6</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T40" t="n">
-        <v>-0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>21</v>
-      </c>
-      <c r="V40" t="n">
-        <v>23</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
-        <v>5.9</v>
+        <v>-33.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3738,55 +3738,55 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>28.5</v>
       </c>
       <c r="E41" t="n">
-        <v>11.3</v>
+        <v>38.7</v>
       </c>
       <c r="F41" t="n">
-        <v>13</v>
+        <v>31.6</v>
       </c>
       <c r="G41" t="n">
-        <v>14.9</v>
+        <v>27.7</v>
       </c>
       <c r="H41" t="n">
-        <v>12.4</v>
+        <v>26.1</v>
       </c>
       <c r="I41" t="n">
-        <v>12.3</v>
+        <v>25.6</v>
       </c>
       <c r="J41" t="n">
-        <v>23.1</v>
+        <v>30</v>
       </c>
       <c r="K41" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="M41" t="n">
         <v>50.6</v>
       </c>
-      <c r="M41" t="n">
-        <v>47.8</v>
-      </c>
       <c r="N41" t="n">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="O41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P41" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.2</v>
+        <v>-2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="U41" t="n">
         <v>21</v>
@@ -3794,19 +3794,15 @@
       <c r="V41" t="n">
         <v>23</v>
       </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>11.3 (3g)</t>
-        </is>
-      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>-0.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3816,75 +3812,79 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F42" t="n">
-        <v>14.2</v>
+        <v>13</v>
       </c>
       <c r="G42" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="H42" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="I42" t="n">
-        <v>13.3</v>
+        <v>12.3</v>
       </c>
       <c r="J42" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="K42" t="n">
-        <v>23.6</v>
+        <v>22.1</v>
       </c>
       <c r="L42" t="n">
-        <v>59.5</v>
+        <v>50.6</v>
       </c>
       <c r="M42" t="n">
-        <v>57.5</v>
+        <v>47.8</v>
       </c>
       <c r="N42" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O42" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P42" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.8</v>
+        <v>-0.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.1</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V42" t="n">
         <v>23</v>
       </c>
-      <c r="W42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>11.3 (3g)</t>
+        </is>
+      </c>
       <c r="X42" t="n">
-        <v>30.1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3894,75 +3894,75 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="E43" t="n">
-        <v>27.3</v>
+        <v>14.7</v>
       </c>
       <c r="F43" t="n">
-        <v>25.4</v>
+        <v>14.2</v>
       </c>
       <c r="G43" t="n">
-        <v>22.1</v>
+        <v>14.6</v>
       </c>
       <c r="H43" t="n">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="I43" t="n">
-        <v>18.2</v>
+        <v>13.3</v>
       </c>
       <c r="J43" t="n">
-        <v>33.2</v>
+        <v>23.5</v>
       </c>
       <c r="K43" t="n">
-        <v>31.7</v>
+        <v>23.6</v>
       </c>
       <c r="L43" t="n">
-        <v>46.8</v>
+        <v>59.5</v>
       </c>
       <c r="M43" t="n">
-        <v>43.6</v>
+        <v>57.5</v>
       </c>
       <c r="N43" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="O43" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P43" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="R43" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="S43" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
-        <v>1.5</v>
+        <v>-0.1</v>
       </c>
       <c r="U43" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V43" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
-        <v>-4.6</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3976,75 +3976,71 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="E44" t="n">
-        <v>15.3</v>
+        <v>27.3</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>25.4</v>
       </c>
       <c r="G44" t="n">
-        <v>12.7</v>
+        <v>22.1</v>
       </c>
       <c r="H44" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
       </c>
       <c r="I44" t="n">
-        <v>10.9</v>
+        <v>18.2</v>
       </c>
       <c r="J44" t="n">
-        <v>27</v>
+        <v>33.2</v>
       </c>
       <c r="K44" t="n">
-        <v>26.4</v>
+        <v>31.7</v>
       </c>
       <c r="L44" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="M44" t="n">
-        <v>45</v>
+        <v>43.6</v>
       </c>
       <c r="N44" t="n">
-        <v>4.2</v>
+        <v>9.5</v>
       </c>
       <c r="O44" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P44" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="R44" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="S44" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="T44" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="U44" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="V44" t="n">
-        <v>23</v>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>10.3 (3g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
-        <v>4.5</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4054,79 +4050,79 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="E45" t="n">
-        <v>13.3</v>
+        <v>15.3</v>
       </c>
       <c r="F45" t="n">
-        <v>12.4</v>
+        <v>14</v>
       </c>
       <c r="G45" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H45" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="I45" t="n">
-        <v>13.1</v>
+        <v>10.9</v>
       </c>
       <c r="J45" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K45" t="n">
-        <v>29.3</v>
+        <v>26.4</v>
       </c>
       <c r="L45" t="n">
-        <v>42.7</v>
+        <v>47.3</v>
       </c>
       <c r="M45" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O45" t="n">
+        <v>80</v>
+      </c>
+      <c r="P45" t="n">
         <v>50</v>
       </c>
-      <c r="P45" t="n">
-        <v>47</v>
-      </c>
       <c r="Q45" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.7</v>
+        <v>3.1</v>
       </c>
       <c r="S45" t="n">
-        <v>-2</v>
+        <v>2.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V45" t="n">
         <v>23</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>19.0 (3g)</t>
+          <t>10.3 (3g)</t>
         </is>
       </c>
       <c r="X45" t="n">
-        <v>12.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4136,157 +4132,157 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="n">
-        <v>24.7</v>
+        <v>13.3</v>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>12.4</v>
       </c>
       <c r="G46" t="n">
-        <v>29.4</v>
+        <v>12.8</v>
       </c>
       <c r="H46" t="n">
-        <v>29.5</v>
+        <v>14.3</v>
       </c>
       <c r="I46" t="n">
-        <v>28.4</v>
+        <v>13.1</v>
       </c>
       <c r="J46" t="n">
-        <v>33.2</v>
+        <v>30</v>
       </c>
       <c r="K46" t="n">
-        <v>33</v>
+        <v>29.3</v>
       </c>
       <c r="L46" t="n">
-        <v>49.9</v>
+        <v>42.7</v>
       </c>
       <c r="M46" t="n">
-        <v>50.4</v>
+        <v>44.7</v>
       </c>
       <c r="N46" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="O46" t="n">
         <v>50</v>
       </c>
       <c r="P46" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.4</v>
+        <v>-0.7</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="T46" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="U46" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V46" t="n">
-        <v>9</v>
-      </c>
-      <c r="W46" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>19.0 (3g)</t>
+        </is>
+      </c>
       <c r="X46" t="n">
-        <v>-13.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>POR @ DEN</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
       <c r="E47" t="n">
-        <v>12.7</v>
+        <v>24.7</v>
       </c>
       <c r="F47" t="n">
-        <v>13.2</v>
+        <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>14.4</v>
+        <v>29.4</v>
       </c>
       <c r="H47" t="n">
-        <v>14.4</v>
+        <v>29.5</v>
       </c>
       <c r="I47" t="n">
-        <v>15.6</v>
+        <v>28.4</v>
       </c>
       <c r="J47" t="n">
-        <v>28.7</v>
+        <v>33.2</v>
       </c>
       <c r="K47" t="n">
-        <v>27.7</v>
+        <v>33</v>
       </c>
       <c r="L47" t="n">
-        <v>44.5</v>
+        <v>49.9</v>
       </c>
       <c r="M47" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="N47" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="O47" t="n">
         <v>50</v>
       </c>
       <c r="P47" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="R47" t="n">
-        <v>-2.4</v>
+        <v>-1.4</v>
       </c>
       <c r="S47" t="n">
         <v>-0.5</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="U47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V47" t="n">
-        <v>17</v>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>12.0 (5g)</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
-        <v>0.2</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4296,79 +4292,79 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="E48" t="n">
-        <v>5.3</v>
+        <v>12.7</v>
       </c>
       <c r="F48" t="n">
-        <v>5.2</v>
+        <v>13.2</v>
       </c>
       <c r="G48" t="n">
-        <v>5.8</v>
+        <v>14.4</v>
       </c>
       <c r="H48" t="n">
-        <v>7.5</v>
+        <v>14.4</v>
       </c>
       <c r="I48" t="n">
-        <v>7.5</v>
+        <v>15.6</v>
       </c>
       <c r="J48" t="n">
-        <v>17.8</v>
+        <v>28.7</v>
       </c>
       <c r="K48" t="n">
-        <v>17.6</v>
+        <v>27.7</v>
       </c>
       <c r="L48" t="n">
-        <v>60.1</v>
+        <v>44.5</v>
       </c>
       <c r="M48" t="n">
-        <v>70.09999999999999</v>
+        <v>45</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="O48" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P48" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="R48" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="S48" t="n">
-        <v>-10</v>
+        <v>-0.5</v>
       </c>
       <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>20</v>
+      </c>
+      <c r="V48" t="n">
+        <v>17</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>12.0 (5g)</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
         <v>0.2</v>
-      </c>
-      <c r="U48" t="n">
-        <v>10</v>
-      </c>
-      <c r="V48" t="n">
-        <v>3</v>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>5.5 (4g)</t>
-        </is>
-      </c>
-      <c r="X48" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4378,79 +4374,79 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="E49" t="n">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="F49" t="n">
-        <v>16.2</v>
+        <v>5.2</v>
       </c>
       <c r="G49" t="n">
-        <v>17.3</v>
+        <v>5.8</v>
       </c>
       <c r="H49" t="n">
-        <v>13.8</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="n">
-        <v>13.3</v>
+        <v>7.5</v>
       </c>
       <c r="J49" t="n">
-        <v>31.7</v>
+        <v>17.8</v>
       </c>
       <c r="K49" t="n">
-        <v>32</v>
+        <v>17.6</v>
       </c>
       <c r="L49" t="n">
-        <v>55.3</v>
+        <v>60.1</v>
       </c>
       <c r="M49" t="n">
-        <v>44.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="O49" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="P49" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q49" t="n">
-        <v>-1.2</v>
+        <v>-0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.9</v>
+        <v>-2.3</v>
       </c>
       <c r="S49" t="n">
-        <v>11.2</v>
+        <v>-10</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="U49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V49" t="n">
         <v>3</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>12.7 (7g)</t>
+          <t>5.5 (4g)</t>
         </is>
       </c>
       <c r="X49" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4460,79 +4456,79 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="E50" t="n">
-        <v>9.699999999999999</v>
+        <v>21</v>
       </c>
       <c r="F50" t="n">
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
       <c r="G50" t="n">
-        <v>12.1</v>
+        <v>17.3</v>
       </c>
       <c r="H50" t="n">
-        <v>12.9</v>
+        <v>13.8</v>
       </c>
       <c r="I50" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="J50" t="n">
-        <v>23.7</v>
+        <v>31.7</v>
       </c>
       <c r="K50" t="n">
-        <v>25.9</v>
+        <v>32</v>
       </c>
       <c r="L50" t="n">
-        <v>39.7</v>
+        <v>55.3</v>
       </c>
       <c r="M50" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="N50" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O50" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P50" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="R50" t="n">
-        <v>-2.3</v>
+        <v>2.9</v>
       </c>
       <c r="S50" t="n">
-        <v>-3.8</v>
+        <v>11.2</v>
       </c>
       <c r="T50" t="n">
-        <v>-2.2</v>
+        <v>-0.3</v>
       </c>
       <c r="U50" t="n">
         <v>20</v>
       </c>
       <c r="V50" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>15.0 (5g)</t>
+          <t>12.7 (7g)</t>
         </is>
       </c>
       <c r="X50" t="n">
-        <v>9.800000000000001</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4542,79 +4538,79 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="E51" t="n">
-        <v>4.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="G51" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H51" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="I51" t="n">
         <v>13.1</v>
       </c>
       <c r="J51" t="n">
-        <v>25.8</v>
+        <v>23.7</v>
       </c>
       <c r="K51" t="n">
-        <v>26.8</v>
+        <v>25.9</v>
       </c>
       <c r="L51" t="n">
-        <v>50</v>
+        <v>39.7</v>
       </c>
       <c r="M51" t="n">
-        <v>50.3</v>
+        <v>43.5</v>
       </c>
       <c r="N51" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="O51" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P51" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="R51" t="n">
-        <v>-6.3</v>
+        <v>-2.3</v>
       </c>
       <c r="S51" t="n">
-        <v>-0.3</v>
+        <v>-3.8</v>
       </c>
       <c r="T51" t="n">
-        <v>-1.1</v>
+        <v>-2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="V51" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>13.2 (6g)</t>
+          <t>15.0 (5g)</t>
         </is>
       </c>
       <c r="X51" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4624,79 +4620,79 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="n">
-        <v>10.3</v>
+        <v>4.7</v>
       </c>
       <c r="F52" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H52" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I52" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K52" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L52" t="n">
+        <v>50</v>
+      </c>
+      <c r="M52" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O52" t="n">
+        <v>50</v>
+      </c>
+      <c r="P52" t="n">
+        <v>53</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="S52" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>10</v>
+      </c>
+      <c r="V52" t="n">
+        <v>3</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>13.2 (6g)</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
         <v>9.1</v>
-      </c>
-      <c r="H52" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J52" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="K52" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="L52" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="M52" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>60</v>
-      </c>
-      <c r="P52" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T52" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="U52" t="n">
-        <v>20</v>
-      </c>
-      <c r="V52" t="n">
-        <v>17</v>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>8.0 (3g)</t>
-        </is>
-      </c>
-      <c r="X52" t="n">
-        <v>13.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4710,55 +4706,55 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>24.5</v>
+        <v>7.5</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>10.3</v>
       </c>
       <c r="F53" t="n">
-        <v>31.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>26.1</v>
+        <v>9.1</v>
       </c>
       <c r="H53" t="n">
-        <v>25.4</v>
+        <v>7.8</v>
       </c>
       <c r="I53" t="n">
-        <v>24.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>37.4</v>
+        <v>20.7</v>
       </c>
       <c r="K53" t="n">
-        <v>35.2</v>
+        <v>23.9</v>
       </c>
       <c r="L53" t="n">
-        <v>50.2</v>
+        <v>48.7</v>
       </c>
       <c r="M53" t="n">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
       <c r="N53" t="n">
-        <v>12.2</v>
+        <v>4.3</v>
       </c>
       <c r="O53" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P53" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="R53" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="S53" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>2.2</v>
+        <v>-3.2</v>
       </c>
       <c r="U53" t="n">
         <v>20</v>
@@ -4768,17 +4764,17 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>25.0 (7g)</t>
+          <t>8.0 (3g)</t>
         </is>
       </c>
       <c r="X53" t="n">
-        <v>7</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4792,55 +4788,55 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>24.5</v>
       </c>
       <c r="E54" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>13.8</v>
+        <v>31.2</v>
       </c>
       <c r="G54" t="n">
-        <v>15.6</v>
+        <v>26.1</v>
       </c>
       <c r="H54" t="n">
-        <v>13.9</v>
+        <v>25.4</v>
       </c>
       <c r="I54" t="n">
-        <v>12.5</v>
+        <v>24.8</v>
       </c>
       <c r="J54" t="n">
-        <v>31.1</v>
+        <v>37.4</v>
       </c>
       <c r="K54" t="n">
-        <v>32.8</v>
+        <v>35.2</v>
       </c>
       <c r="L54" t="n">
-        <v>58</v>
+        <v>50.2</v>
       </c>
       <c r="M54" t="n">
-        <v>51.1</v>
+        <v>46.7</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>12.2</v>
       </c>
       <c r="O54" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P54" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="S54" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="T54" t="n">
-        <v>-1.6</v>
+        <v>2.2</v>
       </c>
       <c r="U54" t="n">
         <v>20</v>
@@ -4850,17 +4846,17 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>15.1 (7g)</t>
+          <t>25.0 (7g)</t>
         </is>
       </c>
       <c r="X54" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4874,75 +4870,75 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="E55" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="F55" t="n">
-        <v>16.4</v>
+        <v>13.8</v>
       </c>
       <c r="G55" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="H55" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="I55" t="n">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="J55" t="n">
-        <v>24.1</v>
+        <v>31.1</v>
       </c>
       <c r="K55" t="n">
-        <v>23.7</v>
+        <v>32.8</v>
       </c>
       <c r="L55" t="n">
-        <v>43.4</v>
+        <v>58</v>
       </c>
       <c r="M55" t="n">
-        <v>41.3</v>
+        <v>51.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="O55" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="P55" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.7</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="S55" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="T55" t="n">
-        <v>0.4</v>
+        <v>-1.6</v>
       </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>10.6 (5g)</t>
+          <t>15.1 (7g)</t>
         </is>
       </c>
       <c r="X55" t="n">
-        <v>-7.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4952,79 +4948,79 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="E56" t="n">
-        <v>14</v>
+        <v>16.7</v>
       </c>
       <c r="F56" t="n">
-        <v>13.2</v>
+        <v>16.4</v>
       </c>
       <c r="G56" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H56" t="n">
         <v>14.3</v>
       </c>
-      <c r="H56" t="n">
-        <v>12.6</v>
-      </c>
       <c r="I56" t="n">
-        <v>12.7</v>
+        <v>13.8</v>
       </c>
       <c r="J56" t="n">
-        <v>29.7</v>
+        <v>24.1</v>
       </c>
       <c r="K56" t="n">
-        <v>30.7</v>
+        <v>23.7</v>
       </c>
       <c r="L56" t="n">
-        <v>51.9</v>
+        <v>43.4</v>
       </c>
       <c r="M56" t="n">
-        <v>47.5</v>
+        <v>41.3</v>
       </c>
       <c r="N56" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="O56" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P56" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="R56" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="S56" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="T56" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="U56" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="V56" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>16.2 (5g)</t>
+          <t>10.6 (5g)</t>
         </is>
       </c>
       <c r="X56" t="n">
-        <v>4.4</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5034,79 +5030,79 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="n">
-        <v>26.7</v>
+        <v>14</v>
       </c>
       <c r="F57" t="n">
-        <v>27.2</v>
+        <v>13.2</v>
       </c>
       <c r="G57" t="n">
-        <v>24</v>
+        <v>14.3</v>
       </c>
       <c r="H57" t="n">
-        <v>25.9</v>
+        <v>12.6</v>
       </c>
       <c r="I57" t="n">
-        <v>26</v>
+        <v>12.7</v>
       </c>
       <c r="J57" t="n">
-        <v>36.1</v>
+        <v>29.7</v>
       </c>
       <c r="K57" t="n">
-        <v>35.5</v>
+        <v>30.7</v>
       </c>
       <c r="L57" t="n">
-        <v>56.7</v>
+        <v>51.9</v>
       </c>
       <c r="M57" t="n">
-        <v>55</v>
+        <v>47.5</v>
       </c>
       <c r="N57" t="n">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="O57" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P57" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R57" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="S57" t="n">
-        <v>1.7</v>
+        <v>4.4</v>
       </c>
       <c r="T57" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="U57" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="V57" t="n">
         <v>17</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>29.2 (6g)</t>
+          <t>16.2 (5g)</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5116,79 +5112,79 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
       <c r="E58" t="n">
-        <v>24.7</v>
+        <v>26.7</v>
       </c>
       <c r="F58" t="n">
-        <v>22.4</v>
+        <v>27.2</v>
       </c>
       <c r="G58" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
       <c r="H58" t="n">
-        <v>19.5</v>
+        <v>25.9</v>
       </c>
       <c r="I58" t="n">
-        <v>22.2</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>31.8</v>
+        <v>36.1</v>
       </c>
       <c r="K58" t="n">
-        <v>31</v>
+        <v>35.5</v>
       </c>
       <c r="L58" t="n">
-        <v>43.5</v>
+        <v>56.7</v>
       </c>
       <c r="M58" t="n">
-        <v>43.4</v>
+        <v>55</v>
       </c>
       <c r="N58" t="n">
-        <v>4.8</v>
+        <v>8.9</v>
       </c>
       <c r="O58" t="n">
         <v>30</v>
       </c>
       <c r="P58" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q58" t="n">
-        <v>-3.3</v>
+        <v>-1.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="S58" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="T58" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="U58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>20.9 (7g)</t>
+          <t>29.2 (6g)</t>
         </is>
       </c>
       <c r="X58" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5198,72 +5194,154 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17.5</v>
+        <v>25.5</v>
       </c>
       <c r="E59" t="n">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
       <c r="F59" t="n">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="G59" t="n">
-        <v>16.2</v>
+        <v>22.8</v>
       </c>
       <c r="H59" t="n">
-        <v>17.6</v>
+        <v>19.5</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>22.2</v>
       </c>
       <c r="J59" t="n">
-        <v>29.9</v>
+        <v>31.8</v>
       </c>
       <c r="K59" t="n">
-        <v>29.3</v>
+        <v>31</v>
       </c>
       <c r="L59" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="M59" t="n">
-        <v>45.7</v>
+        <v>43.4</v>
       </c>
       <c r="N59" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="O59" t="n">
         <v>30</v>
       </c>
       <c r="P59" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.5</v>
+        <v>-3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="S59" t="n">
-        <v>-2.6</v>
+        <v>0.1</v>
       </c>
       <c r="T59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="U59" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V59" t="n">
         <v>3</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
+          <t>20.9 (7g)</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jrue Holiday</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>POR @ DEN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G60" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>17</v>
+      </c>
+      <c r="J60" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="M60" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="N60" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="O60" t="n">
+        <v>30</v>
+      </c>
+      <c r="P60" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U60" t="n">
+        <v>11</v>
+      </c>
+      <c r="V60" t="n">
+        <v>3</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
           <t>14.5 (4g)</t>
         </is>
       </c>
-      <c r="X59" t="n">
+      <c r="X60" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -5278,7 +5356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -5368,7 +5446,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.539</v>
+        <v>0.548</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -5377,20 +5455,20 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4</v>
+        <v>1.364</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.7) — highly predictable output near line — supports the UNDER. H2H avg 1.5 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, Trend, Context, Defense support the UNDER; HR L30, HR L10, H2H dissent. Projection model targets 13.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.7) — highly predictable output near line — supports the UNDER. H2H avg 1.5 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — Volume, Trend, Context, Defense support the UNDER; HR L30, HR L10, H2H dissent. Projection model targets 13.0 pts (1.5 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5494,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.604</v>
+        <v>0.614</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5425,20 +5503,20 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>12.7</v>
+        <v>12.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Anunoby's L30 of 18.5 pts sits 3.0 above the 15.5 line — marginally supports the UNDER. H2H avg 2.8 pts below season L30; TS% shifts -6.3% in this matchup. Opponent is weak defense (#24) at above-average pace (#7). Mixed signals: 2/10 agree (Trend, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 12.7 pts (2.8 pts below line; 60% blended confidence [T3]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
+          <t>Anunoby's L30 of 18.5 pts sits 3.0 above the 15.5 line — marginally supports the UNDER. H2H avg 2.8 pts below season L30; TS% shifts -6.3% in this matchup. Opponent is weak defense (#24) at above-average pace (#7). Mixed signals: 2/10 agree (Trend, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 12.2 pts (3.3 pts below line; 61% blended confidence [T3]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -5464,29 +5542,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.555</v>
+        <v>0.595</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1.357</v>
+        <v>1.417</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Hart averages 16.6 pts in 5 meetings (+4.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#20) at above-average pace (#7). 6/10 signals agree — Context, Defense, H2H, Pace support the OVER; Volume, HR L30, HR L10 dissent. Projection model targets 14.2 pts (1.7 pts above line; 55% blended confidence [T2]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
+          <t>Hart averages 16.6 pts in 5 meetings (+5.1 vs line) — supports the OVER. H2H avg 4.4 pts above season L30; TS% shifts +7.9% in this matchup. Opponent is below-average defense (#20) at above-average pace (#7). 8/10 signals agree — Volume, HR L10, Context, Defense support the OVER; HR L30, Trend dissent. Projection model targets 14.3 pts (2.8 pts above line; 59% blended confidence [T2]). Risk: high variance (σ=7.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5590,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -5521,20 +5599,20 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Alexander-Walker averages 16.5 pts in 4 meetings (-3.0 vs line) — supports the OVER. H2H avg 4.6 pts below season L30; FG% +5.7% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 21.8 pts (2.3 pts above line; 57% blended confidence [T2]).</t>
+          <t>Alexander-Walker averages 16.5 pts in 4 meetings (-3.0 vs line) — supports the OVER. H2H avg 4.6 pts below season L30; FG% +5.7% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; Defense, H2H, Pace dissent. Projection model targets 21.4 pts (1.9 pts above line; 56% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5638,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.539</v>
+        <v>0.512</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -5569,10 +5647,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>2.9</v>
@@ -5582,7 +5660,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Brunson's L30 of 23.2 pts sits 2.3 below the 25.5 line — marginally supports the UNDER. H2H avg 4.0 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 23.9 pts (1.6 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Brunson's L30 of 23.2 pts sits 2.3 below the 25.5 line — marginally supports the UNDER. H2H avg 4.0 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 25.0 pts (0.5 pts below line; 51% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5686,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.711</v>
+        <v>0.698</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -5617,10 +5695,10 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J7" t="n">
         <v>1.87</v>
@@ -5630,7 +5708,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>McCollum averages 10.3 pts in 3 meetings (-7.2 vs line) — marginally supports the UNDER. H2H avg 8.5 pts below season L30; TS% shifts -15.8% in this matchup. Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 4/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.9 pts (8.6 pts below line; 71% blended confidence [T3]).</t>
+          <t>McCollum averages 10.3 pts in 3 meetings (-7.2 vs line) — marginally supports the UNDER. H2H avg 8.5 pts below season L30; TS% shifts -15.8% in this matchup. Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 4/10 agree (Trend, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.4 pts (8.1 pts below line; 69% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5734,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.621</v>
+        <v>0.609</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
@@ -5665,10 +5743,10 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.05</v>
@@ -5678,7 +5756,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Towns averages 29.3 pts in 6 meetings (+9.8 vs line) — supports the OVER. H2H avg 9.9 pts above season L30; TS% shifts +3.6% in this matchup. Opponent is below-average defense (#17) at above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Context, Defense support the OVER; Volume, Trend, FG Trend dissent. Projection model targets 23.8 pts (4.3 pts above line; 62% blended confidence [T2]).</t>
+          <t>Towns averages 29.3 pts in 6 meetings (+9.8 vs line) — supports the OVER. H2H avg 9.9 pts above season L30; TS% shifts +3.6% in this matchup. Opponent is below-average defense (#17) at above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Context, Defense support the OVER; Volume, Trend, FG Trend dissent. Projection model targets 23.3 pts (3.8 pts above line; 60% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -5704,7 +5782,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.517</v>
+        <v>0.543</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
@@ -5713,20 +5791,20 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4</v>
+        <v>1.364</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.0 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.9 pts below season L30; FG% -4.5% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 8.1 pts (0.4 pts below line; 51% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Recent scoring trending down 3.0 pts (L5 vs L30) — marginally supports the UNDER. H2H avg 3.9 pts below season L30; FG% -4.5% trending (L10 vs L30). Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 3/10 agree (Trend, H2H, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 7.0 pts (1.5 pts below line; 54% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
@@ -5748,33 +5826,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.606</v>
+        <v>0.57</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="K10" t="n">
-        <v>1.417</v>
+        <v>1.455</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.6 pts (L5 vs L30) — supports the UNDER. FG% -5.5% trending (L10 vs L30); Minutes down 2.3 recently (L10=19.8 vs L30=22.1). Opponent is strong defense (#8) at slow pace (#28). 7/10 signals agree — HR L30, HR L10, Trend, Defense support the UNDER; Volume, Context, H2H dissent. Projection model targets 7.0 pts (3.5 pts below line; 60% blended confidence [T2]).</t>
+          <t>Recent scoring trending down 2.6 pts (L5 vs L30) — marginally supports the UNDER. FG% -5.5% trending (L10 vs L30); Minutes down 2.3 recently (L10=19.8 vs L30=22.1). Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (Trend, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 6.8 pts (2.7 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5878,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.522</v>
+        <v>0.517</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -5809,20 +5887,20 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>1.364</v>
+        <v>1.435</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Daniels's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. FG% +4.0% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.9 pts (0.6 pts below line; 52% blended confidence [T3]).</t>
+          <t>Daniels's L30 average of 11.9 pts vs the 11.5 line — marginally supports the UNDER. FG% +4.0% trending (L10 vs L30). Opponent is elite defense (#4) at slow pace (#28). Mixed signals: 3/10 agree (Context, Defense, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.1 pts (0.4 pts below line; 51% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5926,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.593</v>
+        <v>0.598</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
@@ -5857,20 +5935,20 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J12" t="n">
         <v>2.7</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K12" t="n">
-        <v>1.333</v>
+        <v>1.435</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Risacher averages 13.2 pts in 6 meetings (+7.7 vs line) — supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 8.2 pts (2.7 pts above line; 59% blended confidence [T2]). Risk: minutes trending down (16.8 L10 vs 20.7 L30) — role reduction would suppress counting stats.</t>
+          <t>Risacher averages 13.2 pts in 6 meetings (+7.7 vs line) — supports the OVER. H2H avg 4.5 pts above season L30; TS% shifts +3.1% in this matchup. Opponent is strong defense (#8) at slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 8.4 pts (2.9 pts above line; 59% blended confidence [T2]). Risk: minutes trending down (16.8 L10 vs 20.7 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5974,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.591</v>
+        <v>0.593</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -5905,20 +5983,20 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.357</v>
+        <v>1.385</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 18.6 pts in 5 meetings (-2.9 vs line) — marginally supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.7% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.9 pts (3.6 pts below line; 59% blended confidence [T3]).</t>
+          <t>Johnson averages 18.6 pts in 5 meetings (-2.9 vs line) — marginally supports the UNDER. H2H avg 3.7 pts below season L30; TS% shifts -5.7% in this matchup. Opponent is strong defense (#8) at slow pace (#28). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.8 pts (3.7 pts below line; 59% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5935,28 +6013,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.524</v>
+        <v>0.538</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>2.8</v>
@@ -5966,7 +6044,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Bridges averages 16.9 pts in 7 meetings (+4.4 vs line) — supports the lean OVER. H2H avg 4.2 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). 8/10 signals agree — Volume, Trend, Context, Defense support the OVER; HR L30, HR L10 dissent. Projection model targets 12.3 pts (0.2 pts below line; 52% blended confidence [T3_LEAN]).</t>
+          <t>Bridges averages 16.9 pts in 7 meetings (+4.4 vs line) — marginally supports the UNDER. H2H avg 4.2 pts above season L30. Opponent is below-average defense (#20) at above-average pace (#7). Mixed signals: 2/10 agree (HR L30, Context); counter-signals: Volume, HR L10, Trend. Projection model targets 11.8 pts (0.7 pts below line; 53% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6070,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.54</v>
+        <v>0.589</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -6001,20 +6079,20 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>20.9</v>
+        <v>18.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.833</v>
+        <v>1.901</v>
       </c>
       <c r="K15" t="n">
-        <v>1.909</v>
+        <v>1.847</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 8.4 pts (L5 vs L30) — supports the UNDER. H2H avg 3.9 pts above season L30; FG% -4.1% trending (L10 vs L30). Opponent is average defense (#14) at moderate pace (#18). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, H2H dissent. Projection model targets 20.9 pts (1.6 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=10.7) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending down 8.4 pts (L5 vs L30) — supports the UNDER. H2H avg 3.9 pts above season L30; FG% -4.1% trending (L10 vs L30). Opponent is average defense (#14) at moderate pace (#18). 7/10 signals agree — HR L10, Trend, Context, Defense support the UNDER; Volume, HR L30, H2H dissent. Projection model targets 18.8 pts (3.7 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=10.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
@@ -6036,23 +6114,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.595</v>
+        <v>0.641</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J16" t="n">
         <v>1.909</v>
@@ -6062,7 +6140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Silva's L30 average of 11.3 pts vs the 9.5 line — marginally supports the OVER. H2H avg 2.1 pts below season L30; TS% shifts +10.5% in this matchup. Opponent is average defense (#14) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 13.0 pts (3.5 pts above line; 59% blended confidence [T3]).</t>
+          <t>Silva's L30 of 11.3 pts sits 2.8 above the 8.5 line — supports the OVER. H2H avg 2.1 pts below season L30; TS% shifts +10.5% in this matchup. Opponent is average defense (#14) at moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, Pace dissent. Projection model targets 13.1 pts (4.6 pts above line; 64% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6166,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.502</v>
+        <v>0.506</v>
       </c>
       <c r="F17" t="n">
         <v>4</v>
@@ -6097,20 +6175,20 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J17" t="n">
         <v>1.952</v>
       </c>
       <c r="K17" t="n">
-        <v>1.769</v>
+        <v>1.8</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Jr. averages 9.2 pts in 5 meetings (-2.3 vs line) — marginally supports the lean UNDER. H2H avg 2.8 pts below season L30; FG% +3.5% trending (L10 vs L30). Opponent is elite defense (#5) at moderate pace (#18). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.5 pts (0.0 pts below line; 50% blended confidence [T3_LEAN]). Risk: L3 has surged to 18.3 after a 20-pt outing (6.3 above L30) — momentum could push over the under line.</t>
+          <t>[Low conviction — lean only] Jr. averages 9.2 pts in 5 meetings (-2.3 vs line) — marginally supports the lean UNDER. H2H avg 2.8 pts below season L30; FG% +3.5% trending (L10 vs L30). Opponent is elite defense (#5) at moderate pace (#18). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.3 pts (0.2 pts below line; 50% blended confidence [T3_LEAN]). Risk: L3 has surged to 18.3 after a 20-pt outing (6.3 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -6132,40 +6210,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.706</v>
+        <v>0.656</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.769</v>
+        <v>1.87</v>
       </c>
       <c r="K18" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Suggs averages 11.7 pts in 6 meetings (-2.8 vs line) — supports the UNDER. TS% shifts -9.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#18). 7/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, FG Trend, Min Trend dissent. Projection model targets 7.3 pts (7.2 pts below line; 70% blended confidence [T1_PREMIUM]).</t>
+          <t>Low scoring variance (σ=4.6) — highly predictable output near line — supports the UNDER. TS% shifts -9.9% in this matchup. Opponent is elite defense (#4) at moderate pace (#18). 6/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, FG Trend dissent. Projection model targets 7.6 pts (5.9 pts below line; 65% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6175,38 +6253,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.591</v>
+        <v>0.555</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>10.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>1.417</v>
+        <v>1.741</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Carter averages 4.2 pts in 5 meetings (-3.3 vs line) — supports the UNDER. H2H avg 2.8 pts below season L30; FG% +4.3% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#18). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; FG Trend, Min Trend dissent. Projection model targets 4.6 pts (2.9 pts below line; 59% blended confidence [T2]).</t>
+          <t>Black's L30 of 16.5 pts sits 8.0 above the 8.5 line — marginally supports the OVER. H2H avg 6.0 pts below season L30; TS% shifts -7.0% in this matchup. Opponent is elite defense (#4) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 10.3 pts (1.8 pts above line; 55% blended confidence [T3]). Risk: L3 has dropped to 5.3 (11.2 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6310,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.548</v>
+        <v>0.546</v>
       </c>
       <c r="F20" t="n">
         <v>4</v>
@@ -6247,10 +6325,10 @@
         <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.909</v>
+        <v>1.952</v>
       </c>
       <c r="K20" t="n">
-        <v>1.833</v>
+        <v>1.8</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -6261,7 +6339,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6280,36 +6358,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.572</v>
+        <v>0.586</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>20.2</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.952</v>
+        <v>1.629</v>
       </c>
       <c r="K21" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Duren averages 14.7 pts in 6 meetings (-7.8 vs line) — marginally supports the UNDER. H2H avg 6.8 pts below season L30; Minutes up 2.8 recently (L10=31.3 vs L30=28.5). Opponent is average defense (#11) at slow pace (#29). Mixed signals: 5/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 20.2 pts (2.3 pts below line; 57% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
+          <t>Reed averages 2.2 pts in 5 meetings (-7.3 vs line) — supports the UNDER. H2H avg 7.0 pts below season L30; TS% shifts +21.9% in this matchup. Opponent is strong defense (#8) at slow pace (#29). 6/10 signals agree — Volume, HR L30, Context, Defense support the UNDER; HR L10, Trend, FG Trend dissent. Projection model targets 6.2 pts (3.3 pts below line; 58% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6324,40 +6402,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.758</v>
+        <v>0.578</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>15.6</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
-        <v>1.741</v>
+        <v>1.826</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1.909</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Jenkins averages 0.7 pts in 3 meetings (-16.8 vs line) — marginally supports the UNDER. H2H avg 10.9 pts below season L30; TS% shifts -38.4% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 1.9 pts (15.6 pts below line; 75% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 8-pt outing (9.4 above L30) — momentum could push over the under line.</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, FG Trend, Min Trend dissent. Projection model targets 8.2 pts (2.3 pts below line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6376,7 +6454,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.549</v>
+        <v>0.628</v>
       </c>
       <c r="F23" t="n">
         <v>6</v>
@@ -6385,27 +6463,27 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>1.833</v>
+        <v>1.87</v>
       </c>
       <c r="K23" t="n">
-        <v>1.909</v>
+        <v>1.87</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the UNDER. H2H avg 1.6 pts above season L30; TS% shifts -5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, FG Trend dissent. Projection model targets 7.8 pts (1.7 pts below line; 54% blended confidence [T3]).</t>
+          <t>Huerter's L30 of 8.2 pts sits 4.3 below the 12.5 line — supports the UNDER. H2H avg 2.8 pts above season L30; TS% shifts +5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, FG Trend dissent. Projection model targets 8.3 pts (4.2 pts below line; 62% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6420,40 +6498,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.603</v>
+        <v>0.769</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>16.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="K24" t="n">
-        <v>1.952</v>
+        <v>1.87</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Robinson averages 7.9 pts in 7 meetings (-2.6 vs line) — marginally supports the UNDER. H2H avg 4.4 pts below season L30; TS% shifts -10.2% in this matchup. Opponent is strong defense (#8) at slow pace (#29). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 6.9 pts (3.6 pts below line; 60% blended confidence [T3]). Risk: 67% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Jenkins averages 0.7 pts in 3 meetings (-18.8 vs line) — supports the UNDER. H2H avg 10.9 pts below season L30; TS% shifts -38.4% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Defense, FG Trend dissent. Projection model targets 2.7 pts (16.8 pts below line; 76% blended confidence [T2]). Risk: L3 has surged to 21.0 after a 8-pt outing (9.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6472,36 +6550,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.575</v>
+        <v>0.55</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
         <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>1.833</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1.909</v>
+        <v>1.769</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Harris's L30 average of 12.8 pts vs the 14.5 line — supports the UNDER. H2H avg 2.4 pts above season L30; TS% shifts +5.3% in this matchup. Opponent is strong defense (#8) at slow pace (#29). 8/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; H2H, FG Trend dissent. Projection model targets 12.6 pts (1.9 pts below line; 57% blended confidence [T3]).</t>
+          <t>Carter averages 4.2 pts in 5 meetings (-2.3 vs line) — marginally supports the UNDER. H2H avg 2.8 pts below season L30; FG% +4.3% trending (L10 vs L30). Opponent is elite defense (#4) at moderate pace (#18). Mixed signals: 5/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 4.6 pts (1.9 pts below line; 55% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6520,41 +6598,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.57</v>
+        <v>0.536</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>20.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="K26" t="n">
-        <v>1.73</v>
+        <v>1.645</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Reed averages 2.2 pts in 5 meetings (-6.3 vs line) — marginally supports the UNDER. H2H avg 7.0 pts below season L30; TS% shifts +21.9% in this matchup. Opponent is strong defense (#8) at slow pace (#29). Mixed signals: 5/10 agree (HR L30, Context, Defense); counter-signals: Volume, HR L10, Trend. Projection model targets 5.6 pts (2.9 pts below line; 57% blended confidence [T3]).</t>
+          <t>Duren averages 14.7 pts in 6 meetings (-6.8 vs line) — marginally supports the UNDER. H2H avg 6.8 pts below season L30; Minutes up 2.8 recently (L10=31.3 vs L30=28.5). Opponent is average defense (#11) at slow pace (#29). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 20.3 pts (1.2 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=7.6) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6568,46 +6646,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.548</v>
+        <v>0.592</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.971</v>
+        <v>2.15</v>
       </c>
       <c r="K27" t="n">
-        <v>1.746</v>
+        <v>1.671</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Huerter's L30 of 8.2 pts sits 2.3 below the 10.5 line — marginally supports the UNDER. H2H avg 2.8 pts above season L30; TS% shifts +5.1% in this matchup. Opponent is below-average defense (#18) at slow pace (#29). Mixed signals: 4/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 8.5 pts (2.0 pts below line; 54% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=5.0) — highly predictable output near line — marginally supports the UNDER. Opponent is average defense (#12) at above-average pace (#10). Mixed signals: 3/10 agree (Context, Defense, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.3 pts (3.2 pts below line; 59% blended confidence [T3]). Risk: 63% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6616,36 +6694,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.752</v>
+        <v>0.653</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>18.4</v>
+        <v>11.9</v>
       </c>
       <c r="I28" t="n">
-        <v>8.9</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>1.769</v>
       </c>
       <c r="K28" t="n">
-        <v>1.357</v>
+        <v>1.952</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Wagner averages 26.2 pts in 4 meetings (+16.7 vs line) — marginally supports the OVER. H2H avg 5.8 pts above season L30; Minutes down 7.9 recently (L10=22.5 vs L30=30.4). Opponent is average defense (#14) at moderate pace (#18). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 18.4 pts (8.9 pts above line; 75% blended confidence [T3]). Risk: L3 has dropped to 13.7 (6.7 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Merrill averages 10.0 pts in 3 meetings (-6.5 vs line) — supports the UNDER. H2H avg 2.1 pts below season L30; TS% shifts +12.4% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, Pace, Min Trend dissent. Projection model targets 11.9 pts (4.6 pts below line; 65% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6655,7 +6733,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6664,36 +6742,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.537</v>
+        <v>0.746</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>21.4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>11.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>1.926</v>
       </c>
       <c r="K29" t="n">
-        <v>1.408</v>
+        <v>1.833</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Mobley averages 23.0 pts in 3 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 4.5 pts above season L30; FG% +4.5% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 4/10 agree (Defense, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 21.4 pts (1.9 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
+          <t>Jackson's L30 average of 16.5 pts vs the 16.5 line — marginally supports the UNDER. Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 3/10 agree (HR L30, Context, FG Trend); counter-signals: Volume, HR L10, Trend. Projection model targets 5.0 pts (11.5 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 21.3 after a 28-pt outing (4.8 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6712,36 +6790,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.733</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>17.6</v>
+        <v>5.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="J30" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="K30" t="n">
-        <v>1.385</v>
+        <v>1.658</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.2 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 1/10 agree (Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 17.6 pts (1.9 pts below line; 56% blended confidence [T3]).</t>
+          <t>Ellis averages 5.4 pts in 5 meetings (-8.1 vs line) — marginally supports the UNDER. H2H avg 2.9 pts below season L30; TS% shifts -3.5% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 5.7 pts (7.8 pts below line; 73% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6751,7 +6829,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6760,36 +6838,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.542</v>
+        <v>0.505</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>14.7</v>
+        <v>21.7</v>
       </c>
       <c r="I31" t="n">
         <v>0.2</v>
       </c>
       <c r="J31" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="K31" t="n">
-        <v>1.435</v>
+        <v>1.952</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Allen's L30 of 16.6 pts sits 2.1 above the 14.5 line — supports the lean OVER. H2H avg 1.6 pts below season L30; FG% +3.8% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). 8/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Min Trend dissent. Projection model targets 14.7 pts (0.2 pts above line; 54% blended confidence [T3_LEAN]).</t>
+          <t>[Low conviction — lean only] Mobley's L30 of 18.5 pts sits 3.0 below the 21.5 line — supports the lean UNDER. H2H avg 4.5 pts above season L30; FG% +4.5% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). 6/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 21.7 pts (0.2 pts above line; 50% blended confidence [T3_LEAN]). Risk: high variance (σ=8.8) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6808,36 +6886,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.536</v>
+        <v>0.697</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="J32" t="n">
-        <v>1.87</v>
+        <v>1.769</v>
       </c>
       <c r="K32" t="n">
-        <v>1.855</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 4.8 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#22) at above-average pace (#6). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 9.8 pts (1.7 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=10.0) makes the outcome difficult to call with confidence.</t>
+          <t>Schröder's L30 of 8.2 pts sits 6.3 below the 14.5 line — supports the UNDER. H2H avg 6.5 pts above season L30; TS% shifts +5.2% in this matchup. Opponent is below-average defense (#22) at above-average pace (#6). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the UNDER; Defense, H2H, Pace dissent. Projection model targets 8.8 pts (5.7 pts below line; 69% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6847,7 +6925,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6856,41 +6934,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.536</v>
+        <v>0.554</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>27.4</v>
+        <v>14.4</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1.833</v>
       </c>
       <c r="K33" t="n">
-        <v>1.364</v>
+        <v>1.909</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 3.4 pts (L5 vs L30) — supports the OVER. Opponent is below-average defense (#22) at above-average pace (#6). 6/10 signals agree — Volume, HR L10, Context, Defense support the OVER; HR L30, Trend, H2H dissent. Projection model targets 27.4 pts (1.9 pts above line; 53% blended confidence [T3]). Risk: high variance (σ=11.4) makes the outcome difficult to call with confidence.</t>
+          <t>Allen's L30 average of 16.6 pts vs the 15.5 line — marginally supports the UNDER. H2H avg 1.6 pts below season L30; FG% +3.8% trending (L10 vs L30). Opponent is weak defense (#23) at above-average pace (#6). Mixed signals: 3/10 agree (Trend, H2H, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 14.4 pts (1.1 pts below line; 55% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6904,7 +6982,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.545</v>
+        <v>0.571</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
@@ -6913,27 +6991,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
-        <v>2.9</v>
+        <v>1.877</v>
       </c>
       <c r="K34" t="n">
-        <v>1.385</v>
+        <v>1.877</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Jr.'s L30 of 14.5 pts sits 4.0 above the 10.5 line — marginally supports the UNDER. Minutes down 2.5 recently (L10=29.0 vs L30=31.5). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.2 pts (1.3 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=9.3) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 4.7 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#16) at above-average pace (#10). Mixed signals: 3/10 agree (Context, FG Trend, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.8 pts (1.7 pts below line; 57% blended confidence [T3]). Risk: 60% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6952,19 +7030,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>16.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>2.9</v>
@@ -6974,14 +7052,14 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the UNDER. TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 16.2 pts (2.3 pts below line; 56% blended confidence [T3]).</t>
+          <t>Jr.'s L30 of 14.5 pts sits 4.0 above the 10.5 line — marginally supports the UNDER. Minutes down 2.5 recently (L10=29.0 vs L30=31.5). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 9.7 pts (0.8 pts below line; 53% blended confidence [T3]). Risk: high variance (σ=9.3) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7000,36 +7078,36 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.741</v>
+        <v>0.545</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.8</v>
+        <v>15.8</v>
       </c>
       <c r="I36" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J36" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="K36" t="n">
-        <v>1.87</v>
+        <v>1.345</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Edgecombe's L30 of 16.9 pts sits 4.4 above the 12.5 line — marginally supports the UNDER. FG% +6.3% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 3.8 pts (8.7 pts below line; 74% blended confidence [T3]). Risk: high variance (σ=10.2) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the UNDER. TS% shifts +11.2% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 6/10 signals agree — Volume, HR L30, Context, H2H support the UNDER; HR L10, Trend, Defense dissent. Projection model targets 15.8 pts (1.7 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7048,7 +7126,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.532</v>
+        <v>0.772</v>
       </c>
       <c r="F37" t="n">
         <v>3</v>
@@ -7057,27 +7135,27 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>24.3</v>
+        <v>2.1</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>10.4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="K37" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.1) — highly predictable output near line — marginally supports the UNDER. Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, Defense); counter-signals: Volume, HR L30, HR L10. Projection model targets 24.3 pts (1.2 pts below line; 53% blended confidence [T3]).</t>
+          <t>Edgecombe's L30 of 16.9 pts sits 4.4 above the 12.5 line — marginally supports the UNDER. FG% +6.3% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.1 pts (10.4 pts below line; 77% blended confidence [T3]). Risk: high variance (σ=10.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7087,7 +7165,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7096,7 +7174,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.543</v>
+        <v>0.548</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
@@ -7105,27 +7183,27 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>14.1</v>
+        <v>26.1</v>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="K38" t="n">
-        <v>1.417</v>
+        <v>1.345</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Fox averages 21.7 pts in 3 meetings (+6.2 vs line) — supports the UNDER. H2H avg 5.4 pts above season L30; TS% shifts +15.1% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, H2H dissent. Projection model targets 14.1 pts (1.4 pts below line; 54% blended confidence [T3]).</t>
+          <t>Low scoring variance (σ=4.1) — highly predictable output near line — supports the OVER. Opponent is strong defense (#8) at above-average pace (#9). 7/10 signals agree — Volume, HR L30, HR L10, Context support the OVER; Trend, Defense, H2H dissent. Projection model targets 26.1 pts (1.6 pts above line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7144,36 +7222,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.587</v>
+        <v>0.569</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 2.5 recently (L10=22.1 vs L30=24.6). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.9 pts (2.6 pts below line; 58% blended confidence [T3]). Risk: 73% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
+          <t>Fox averages 21.7 pts in 3 meetings (+6.2 vs line) — supports the UNDER. H2H avg 5.4 pts above season L30; TS% shifts +15.1% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Defense, H2H dissent. Projection model targets 13.0 pts (2.5 pts below line; 56% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7192,36 +7270,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.745</v>
+        <v>0.592</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>16.5</v>
+        <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 6.0 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 16.5 pts (12.0 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 38.7 after a 21-pt outing (13.1 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — marginally supports the UNDER. FG% +6.7% trending (L10 vs L30); Minutes down 2.5 recently (L10=22.1 vs L30=24.6). Opponent is strong defense (#8) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Defense, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 2.7 pts (2.8 pts below line; 59% blended confidence [T3]). Risk: 73% over-rate on L30 suggests scoring tendency that could threaten the under.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7240,7 +7318,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.548</v>
+        <v>0.74</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
@@ -7249,27 +7327,27 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>10.9</v>
+        <v>18.7</v>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>1.357</v>
+        <v>1.364</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>Johnson's L30 average of 12.3 pts vs the 12.5 line — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.9 pts (1.6 pts below line; 54% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 6.0 pts (L5 vs L30) — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 18.7 pts (9.8 pts below line; 74% blended confidence [T3]). Risk: L3 has surged to 38.7 after a 21-pt outing (13.1 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7279,45 +7357,45 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.756</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9.300000000000001</v>
-      </c>
       <c r="J42" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K42" t="n">
-        <v>1.4</v>
+        <v>1.435</v>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 13.3 pts vs the 11.5 line — supports the OVER. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, Min Trend dissent. Projection model targets 20.8 pts (9.3 pts above line; 75% blended confidence [T1_PREMIUM]).</t>
+          <t>Johnson's L30 average of 12.3 pts vs the 12.5 line — marginally supports the UNDER. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 10.5 pts (2.0 pts below line; 55% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7332,40 +7410,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.555</v>
+        <v>0.732</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>8.4</v>
       </c>
       <c r="J43" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>1.4</v>
+        <v>1.364</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. FG% +3.2% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 19.4 pts (1.9 pts above line; 55% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
+          <t>Harper's L30 average of 13.3 pts vs the 11.5 line — supports the OVER. Opponent is below-average defense (#16) at slow pace (#23). 7/10 signals agree — Volume, HR L30, HR L10, Trend support the OVER; H2H, Pace, Min Trend dissent. Projection model targets 19.9 pts (8.4 pts above line; 73% blended confidence [T1_PREMIUM]).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7384,7 +7462,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.537</v>
+        <v>0.519</v>
       </c>
       <c r="F44" t="n">
         <v>7</v>
@@ -7393,10 +7471,10 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>11</v>
+        <v>17.9</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>3.1</v>
@@ -7406,14 +7484,14 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — supports the OVER. TS% shifts +4.5% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, H2H, Pace dissent. Projection model targets 11.0 pts (0.5 pts above line; 53% blended confidence [T3]).</t>
+          <t>Recent scoring trending up 7.2 pts (L5 vs L30) — supports the OVER. FG% +3.2% trending (L10 vs L30). Opponent is strong defense (#8) at above-average pace (#9). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Defense, H2H dissent. Projection model targets 17.9 pts (0.4 pts above line; 51% blended confidence [T3]). Risk: high variance (σ=9.5) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7423,45 +7501,45 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.503</v>
+        <v>0.536</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>13.6</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="K45" t="n">
-        <v>1.345</v>
+        <v>1.417</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Vassell averages 19.0 pts in 3 meetings (+5.5 vs line) — marginally supports the lean OVER. H2H avg 5.9 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 4/10 agree (Context, Defense, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.6 pts (0.1 pts above line; 50% blended confidence [T3_LEAN]).</t>
+          <t>Recent scoring trending up 3.1 pts (L5 vs L30) — marginally supports the UNDER. TS% shifts +4.5% in this matchup. Opponent is below-average defense (#21) at slow pace (#23). Mixed signals: 3/10 agree (Context, H2H, Pace); counter-signals: Volume, HR L30, HR L10. Projection model targets 10.0 pts (0.5 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 15.3 after a 26-pt outing (4.4 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7471,50 +7549,50 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.753</v>
+        <v>0.515</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="I46" t="n">
-        <v>14.3</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K46" t="n">
-        <v>1.385</v>
+        <v>1.408</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Embiid's L30 average of 28.4 pts vs the 27.5 line — marginally supports the UNDER. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.2 pts (14.3 pts below line; 75% blended confidence [T3]).</t>
+          <t>[Low conviction — lean only] Vassell averages 19.0 pts in 3 meetings (+6.5 vs line) — marginally supports the lean OVER. H2H avg 5.9 pts above season L30; TS% shifts +12.7% in this matchup. Opponent is below-average defense (#16) at slow pace (#23). Mixed signals: 5/10 agree (Volume, Context, Defense); counter-signals: HR L30, HR L10, Trend. Projection model targets 12.8 pts (0.3 pts above line; 51% blended confidence [T3_LEAN]).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>POR @ DEN</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7528,36 +7606,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.609</v>
+        <v>0.753</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>11.1</v>
+        <v>13</v>
       </c>
       <c r="I47" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Gordon averages 12.0 pts in 5 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 3.6 pts below season L30. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.1 pts (4.4 pts below line; 60% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
+          <t>Embiid's L30 average of 28.4 pts vs the 27.5 line — marginally supports the UNDER. Opponent is below-average defense (#18) at above-average pace (#9). Mixed signals: 3/10 agree (Trend, Context, FG Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 13.0 pts (14.5 pts below line; 75% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7576,36 +7654,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.57</v>
+        <v>0.611</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="I48" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J48" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="K48" t="n">
-        <v>1.455</v>
+        <v>1.435</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — supports the UNDER. H2H avg 2.0 pts below season L30; TS% shifts +3.5% in this matchup. Opponent is strong defense (#10) at fast pace (#3). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Pace, Min Trend dissent. Projection model targets 5.7 pts (1.8 pts below line; 56% blended confidence [T3]).</t>
+          <t>Gordon averages 12.0 pts in 5 meetings (-3.5 vs line) — marginally supports the UNDER. H2H avg 3.6 pts below season L30. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Trend, Context, H2H); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.0 pts (4.5 pts below line; 61% blended confidence [T3]). Risk: high variance (σ=7.7) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7624,36 +7702,36 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.541</v>
+        <v>0.57</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>12.8</v>
+        <v>5.6</v>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="K49" t="n">
-        <v>1.364</v>
+        <v>1.455</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending up 2.9 pts (L5 vs L30) — marginally supports the UNDER. FG% +11.2% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.8 pts (1.7 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 11-pt outing (7.7 above L30) — momentum could push over the under line.</t>
+          <t>Recent scoring trending down 2.3 pts (L5 vs L30) — supports the UNDER. H2H avg 2.0 pts below season L30; TS% shifts +3.5% in this matchup. Opponent is strong defense (#10) at fast pace (#3). 7/10 signals agree — HR L30, HR L10, Trend, Context support the UNDER; Volume, Pace, Min Trend dissent. Projection model targets 5.6 pts (1.9 pts below line; 57% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7663,7 +7741,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7672,7 +7750,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.576</v>
+        <v>0.549</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -7681,27 +7759,27 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>14.5</v>
+        <v>12.4</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K50" t="n">
-        <v>1.345</v>
+        <v>1.408</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Jr. averages 15.0 pts in 5 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +9.8% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 14.5 pts (3.0 pts above line; 57% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
+          <t>Recent scoring trending up 2.9 pts (L5 vs L30) — marginally supports the UNDER. FG% +11.2% trending (L10 vs L30). Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 12.4 pts (2.1 pts below line; 54% blended confidence [T3]). Risk: L3 has surged to 21.0 after a 11-pt outing (7.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7720,7 +7798,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.573</v>
+        <v>0.583</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -7729,27 +7807,27 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
       <c r="I51" t="n">
         <v>3.3</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K51" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>Recent scoring trending down 6.3 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +9.1% in this matchup. Opponent is strong defense (#10) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 15.8 pts (3.3 pts above line; 57% blended confidence [T3]). Risk: L3 has dropped to 4.7 (8.4 below L30) — deepening slump makes the over vulnerable.</t>
+          <t>Jr. averages 15.0 pts in 5 meetings (+3.5 vs line) — marginally supports the OVER. H2H avg 1.9 pts above season L30; TS% shifts +9.8% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Pace. Projection model targets 14.8 pts (3.3 pts above line; 58% blended confidence [T3]). Risk: high variance (σ=7.1) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7768,19 +7846,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.54</v>
+        <v>0.599</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>8.800000000000001</v>
+        <v>16.9</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>2.8</v>
@@ -7790,14 +7868,14 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>Low scoring variance (σ=4.3) — highly predictable output near line — supports the OVER. TS% shifts +13.9% in this matchup; Minutes down 3.2 recently (L10=20.7 vs L30=23.9). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 8.8 pts (1.3 pts above line; 54% blended confidence [T3]). Risk: minutes trending down (20.7 L10 vs 23.9 L30) — role reduction would suppress counting stats.</t>
+          <t>Recent scoring trending down 6.3 pts (L5 vs L30) — marginally supports the OVER. TS% shifts +9.1% in this matchup. Opponent is strong defense (#10) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, Context); counter-signals: HR L10, Trend, Defense. Projection model targets 16.9 pts (4.4 pts above line; 59% blended confidence [T3]). Risk: L3 has dropped to 4.7 (8.4 below L30) — deepening slump makes the over vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7807,16 +7885,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.514</v>
+        <v>0.535</v>
       </c>
       <c r="F53" t="n">
         <v>7</v>
@@ -7825,27 +7903,27 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>24.4</v>
+        <v>8.6</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K53" t="n">
-        <v>1.357</v>
+        <v>1.408</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Recent scoring trending up 6.4 pts (L5 vs L30) — supports the lean OVER. TS% shifts +7.0% in this matchup; FG% +3.5% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, Trend, Context, Defense support the OVER; HR L30, HR L10, Pace dissent. Projection model targets 24.4 pts (0.1 pts below line; 51% blended confidence [T3_LEAN]). Risk: high variance (σ=12.2) makes the outcome difficult to call with confidence.</t>
+          <t>Low scoring variance (σ=4.3) — highly predictable output near line — supports the OVER. TS% shifts +13.9% in this matchup; Minutes down 3.2 recently (L10=20.7 vs L30=23.9). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 8.6 pts (1.1 pts above line; 53% blended confidence [T3]). Risk: minutes trending down (20.7 L10 vs 23.9 L30) — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7855,45 +7933,45 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="F54" t="n">
         <v>7</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>12.7</v>
+        <v>24.5</v>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="K54" t="n">
         <v>1.8</v>
       </c>
-      <c r="K54" t="n">
-        <v>1.952</v>
-      </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Braun averages 15.1 pts in 7 meetings (+3.6 vs line) — supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +8.3% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 12.7 pts (1.2 pts above line; 56% blended confidence [T2]).</t>
+          <t>[Low conviction — lean only] Recent scoring trending up 6.4 pts (L5 vs L30) — supports the lean OVER. TS% shifts +7.0% in this matchup; FG% +3.5% trending (L10 vs L30). Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, Trend, Context, Defense support the OVER; HR L30, HR L10, Pace dissent. Projection model targets 24.5 pts (0.0 pts below line; 51% blended confidence [T3_LEAN]). Risk: high variance (σ=12.2) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7903,7 +7981,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7912,36 +7990,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.582</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>11.4</v>
+        <v>12.7</v>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="K55" t="n">
-        <v>1.364</v>
+        <v>1.4</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Henderson averages 10.6 pts in 5 meetings (-3.9 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace, FG Trend dissent. Projection model targets 11.4 pts (3.1 pts below line; 58% blended confidence [T2]).</t>
+          <t>Braun averages 15.1 pts in 7 meetings (+3.6 vs line) — supports the OVER. H2H avg 2.6 pts above season L30; TS% shifts +8.3% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). 7/10 signals agree — Volume, HR L10, Trend, Context support the OVER; HR L30, Pace, Min Trend dissent. Projection model targets 12.7 pts (1.2 pts above line; 55% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7956,23 +8034,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.538</v>
+        <v>0.574</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>11.7</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
@@ -7982,14 +8060,14 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Johnson averages 16.2 pts in 5 meetings (+3.7 vs line) — marginally supports the UNDER. H2H avg 3.5 pts above season L30; TS% shifts +4.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 3/10 agree (Context, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.7 pts (0.8 pts below line; 53% blended confidence [T3]).</t>
+          <t>Henderson averages 10.6 pts in 5 meetings (-3.9 vs line) — supports the UNDER. H2H avg 3.2 pts below season L30; TS% shifts -7.3% in this matchup. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L30, HR L10, Context support the UNDER; Trend, Pace, FG Trend dissent. Projection model targets 11.7 pts (2.8 pts below line; 57% blended confidence [T2]).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8008,36 +8086,36 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.545</v>
+        <v>0.541</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>25.3</v>
+        <v>11.6</v>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K57" t="n">
-        <v>1.364</v>
+        <v>1.357</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Jokić's L30 average of 26.0 pts vs the 27.5 line — marginally supports the UNDER. H2H avg 3.2 pts above season L30; TS% shifts +6.2% in this matchup. Opponent is weak defense (#28) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 25.3 pts (2.2 pts below line; 54% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
+          <t>Johnson averages 16.2 pts in 5 meetings (+3.7 vs line) — marginally supports the UNDER. H2H avg 3.5 pts above season L30; TS% shifts +4.4% in this matchup. Opponent is below-average defense (#20) at moderate pace (#17). Mixed signals: 3/10 agree (Context, Pace, Min Trend); counter-signals: Volume, HR L30, HR L10. Projection model targets 11.6 pts (0.9 pts below line; 54% blended confidence [T3]).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8056,7 +8134,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.579</v>
+        <v>0.581</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -8065,27 +8143,27 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K58" t="n">
-        <v>1.408</v>
+        <v>1.345</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Avdija averages 20.9 pts in 7 meetings (-4.6 vs line) — marginally supports the UNDER. TS% shifts +7.4% in this matchup. Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 23.7 pts (1.8 pts below line; 57% blended confidence [T3]).</t>
+          <t>Jokić's L30 average of 26.0 pts vs the 27.5 line — marginally supports the UNDER. H2H avg 3.2 pts above season L30; TS% shifts +6.2% in this matchup. Opponent is weak defense (#28) at moderate pace (#17). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, H2H. Projection model targets 23.8 pts (3.7 pts below line; 58% blended confidence [T3]). Risk: high variance (σ=8.9) makes the outcome difficult to call with confidence.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8104,29 +8182,77 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.536</v>
+        <v>0.578</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>16.2</v>
+        <v>23.7</v>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J59" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K59" t="n">
-        <v>1.385</v>
+        <v>1.333</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Holiday averages 14.5 pts in 4 meetings (-3.0 vs line) — supports the UNDER. H2H avg 2.5 pts below season L30. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, Pace dissent. Projection model targets 16.2 pts (1.3 pts below line; 53% blended confidence [T3]). Risk: L3 has surged to 22.7 after a 22-pt outing (5.7 above L30) — momentum could push over the under line.</t>
+          <t>Avdija averages 20.9 pts in 7 meetings (-4.6 vs line) — marginally supports the UNDER. TS% shifts +7.4% in this matchup. Opponent is below-average defense (#20) at fast pace (#3). Mixed signals: 5/10 agree (Volume, HR L30, HR L10); counter-signals: Trend, Defense, Pace. Projection model targets 23.7 pts (1.8 pts below line; 57% blended confidence [T3]).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jrue Holiday</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>POR @ DEN</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Holiday averages 14.5 pts in 4 meetings (-3.0 vs line) — supports the UNDER. H2H avg 2.5 pts below season L30. Opponent is average defense (#11) at fast pace (#3). 6/10 signals agree — Volume, HR L10, Context, Defense support the UNDER; HR L30, Trend, Pace dissent. Projection model targets 15.6 pts (1.9 pts below line; 55% blended confidence [T2]). Risk: L3 has surged to 22.7 after a 22-pt outing (5.7 above L30) — momentum could push over the under line.</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8253,7 +8379,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
@@ -8373,7 +8499,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="11">
@@ -8449,7 +8575,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -8493,7 +8619,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="17">
@@ -8533,13 +8659,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jevon Carter</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8549,11 +8675,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="20">
@@ -8579,7 +8705,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jalen Duren</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8593,13 +8719,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -8613,13 +8739,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Kevin Huerter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8633,13 +8759,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8653,13 +8779,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Jevon Carter</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8673,13 +8799,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Jalen Duren</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8693,18 +8819,18 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kevin Huerter</t>
+          <t>Cedric Coward</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8713,33 +8839,33 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Franz Wagner</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DET @ ORL</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>GG Jackson</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8749,17 +8875,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Keon Ellis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8773,13 +8899,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8789,17 +8915,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Max Strus</t>
+          <t>Dennis Schröder</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8813,13 +8939,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8829,22 +8955,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kelly Oubre Jr.</t>
+          <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PHI @ SAS</t>
+          <t>CLE @ MEM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8853,13 +8979,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Kelly Oubre Jr.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8873,13 +8999,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8893,13 +9019,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8913,13 +9039,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>25.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8929,17 +9055,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8953,13 +9079,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8973,13 +9099,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>28.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8993,13 +9119,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9009,17 +9135,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paul George</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9033,13 +9159,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Paul George</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9053,13 +9179,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9069,17 +9195,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9089,22 +9215,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aaron Gordon</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>POR @ DEN</t>
+          <t>PHI @ SAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9113,13 +9239,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Aaron Gordon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9133,13 +9259,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9153,13 +9279,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9169,17 +9295,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9193,13 +9319,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bruce Brown</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9213,13 +9339,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Bruce Brown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9229,17 +9355,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>24.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9249,17 +9375,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9269,17 +9395,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cameron Johnson</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9293,13 +9419,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Nikola Jokić</t>
+          <t>Cameron Johnson</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9313,13 +9439,13 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Nikola Jokić</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9333,26 +9459,46 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>Deni Avdija</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>POR @ DEN</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D60" t="n">
         <v>17.5</v>
       </c>
     </row>

--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +75,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1194,7 +1206,7 @@
         <v>-4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1284,7 +1296,6 @@
       <c r="V10" t="n">
         <v>28</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-6.4</v>
       </c>
@@ -2674,7 +2685,6 @@
       <c r="V27" t="n">
         <v>10</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>-1.7</v>
       </c>
@@ -2834,7 +2844,6 @@
       <c r="V29" t="n">
         <v>10</v>
       </c>
-      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>-36.8</v>
       </c>
@@ -3240,7 +3249,6 @@
       <c r="V34" t="n">
         <v>10</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-21.9</v>
       </c>
@@ -3318,7 +3326,6 @@
       <c r="V35" t="n">
         <v>9</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-17.8</v>
       </c>
@@ -3478,7 +3485,6 @@
       <c r="V37" t="n">
         <v>9</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>-25.8</v>
       </c>
@@ -3556,7 +3562,6 @@
       <c r="V38" t="n">
         <v>9</v>
       </c>
-      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>-2</v>
       </c>
@@ -3716,7 +3721,6 @@
       <c r="V40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-33.6</v>
       </c>
@@ -3786,7 +3790,7 @@
         <v>0.3</v>
       </c>
       <c r="T41" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>21</v>
@@ -3794,7 +3798,6 @@
       <c r="V41" t="n">
         <v>23</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>5.9</v>
       </c>
@@ -3954,7 +3957,6 @@
       <c r="V43" t="n">
         <v>23</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>30.1</v>
       </c>
@@ -4032,7 +4034,6 @@
       <c r="V44" t="n">
         <v>9</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-4.6</v>
       </c>
@@ -4274,7 +4275,6 @@
       <c r="V47" t="n">
         <v>9</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>-13.1</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>40</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>-2.3</v>
@@ -8323,1183 +8323,2717 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Okongwu scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Okongwu played 37 min (+7.6 vs L10 avg of 29.1) — 26% more than expected. Shooting efficiency was cold: 30.8% FG (-15.7% vs L10 avg of 46.5%). 4/13 from the field. Signals that called it correctly: Volume, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, HR L10, H2H. Projection model targeted 13.0 pts — actual 12 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Okongwu in this role.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 22 pts vs 15.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 37 played vs L10 avg 34.2. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 49.0%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend. Projection model targeted 12.2 pts — actual 22 was 9.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Anunoby's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hart scored 2 pts vs 11.5 line (-9.5), OVER missed by 9.5 pts. Minutes were as expected: 31 played vs L10 avg 31.5. Shooting efficiency was cold: 33.3% FG (-24.5% vs L10 avg of 57.8%). 1/3 from the field. Counter-signals that proved correct: HR L30, Trend. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 14.3 pts — actual 2 was 12.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Alexander-Walker scored 36 pts vs 19.5 line (+16.5), OVER hit by 16.5 pts. Alexander-Walker played 39 min (+6.2 vs L10 avg of 32.8) — 19% more than expected. Shooting efficiency was hot: 63.2% FG (+10.5% vs L10 avg of 52.7%). 12/19 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 21.4 pts — actual 36 was 14.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Alexander-Walker's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brunson scored 30 pts vs 25.5 line (+4.5), UNDER missed by 4.5 pts. Brunson played 39 min (+3.4 vs L10 avg of 35.8) — 9% more than expected. Shooting was in line with averages: 42.3% FG (11/26, L10 avg 45.9%). Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 25.0 pts — actual 30 was 5.0 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Brunson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN — McCollum scored 17 pts vs 17.5 line (-0.5), UNDER hit by 0.5 pts. McCollum played 35 min (+5.4 vs L10 avg of 29.2) — 18% more than expected. Shooting efficiency was cold: 36.8% FG (-14.1% vs L10 avg of 50.9%). 7/19 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.4 pts — actual 17 was 7.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms McCollum's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Towns scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 29.2. Shooting efficiency was hot: 75.0% FG (+20.1% vs L10 avg of 54.9%). 9/12 from the field. Signals that called it correctly: HR L30, HR L10, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: Volume, Trend, FG Trend. Projection model targeted 23.3 pts — actual 21 was 2.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Towns's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Landry Shamet</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Shamet scored 1 pts vs 8.5 line (-7.5), UNDER hit by 7.5 pts. Shamet played 21 min (-3.3 vs L10 avg of 24.5) — 13% less than expected. Shooting efficiency was cold: 0.0% FG (-39.2% vs L10 avg of 39.2%). 0/2 from the field. Signals that called it correctly: Trend, H2H, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.0 pts — actual 1 was 6.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Shamet's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Kuminga scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 22 played vs L10 avg 19.8. Shooting was in line with averages: 33.3% FG (2/6, L10 avg 38.2%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.8 pts — actual 5 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Kuminga in this role.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Daniels scored 11 pts vs 11.5 line (-0.5), UNDER hit by 0.5 pts. Daniels played 38 min (+5.7 vs L10 avg of 32.2) — 18% more than expected. Shooting efficiency was cold: 36.4% FG (-20.0% vs L10 avg of 56.4%). 4/11 from the field. Signals that called it correctly: Context, Defense, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.1 pts — actual 11 was 0.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Daniels in this role.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Risacher scored 3 pts vs 5.5 line (-2.5), OVER missed by 2.5 pts. Risacher played 7 min (-9.4 vs L10 avg of 16.8) — 56% less than expected. Shooting efficiency was cold: 25.0% FG (-35.7% vs L10 avg of 60.7%). 1/4 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.4 pts — actual 3 was 5.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Risacher for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 21 pts vs 21.5 line (-0.5), UNDER hit by 0.5 pts. Johnson played 41 min (+5.2 vs L10 avg of 35.4) — 15% more than expected. Shooting efficiency was cold: 42.1% FG (-6.5% vs L10 avg of 48.6%). 8/19 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.8 pts — actual 21 was 3.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Johnson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 15 pts vs 12.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 32 played vs L10 avg 31.5. Shooting efficiency was hot: 53.8% FG (+6.3% vs L10 avg of 47.5%). 7/13 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context. Projection model targeted 11.8 pts — actual 15 was 3.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 31 pts vs 22.5 line (+8.5), UNDER missed by 8.5 pts. Banchero played 38 min (+3.6 vs L10 avg of 34.1) — 11% more than expected. Shooting efficiency was hot: 62.5% FG (+22.8% vs L10 avg of 39.7%). 10/16 from the field. Counter-signals that proved correct: Volume, HR L30, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 18.8 pts — actual 31 was 12.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 12 pts vs 8.5 line (+3.5), OVER hit by 3.5 pts. Silva played 33 min (+6.8 vs L10 avg of 26.4) — 26% more than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 45.6%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 13.1 pts — actual 12 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Silva in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 12 pts vs 11.5 line (+0.5), UNDER missed by 0.5 pts. Jr. played 18 min (-11.3 vs L10 avg of 29.7) — 38% less than expected. Shooting efficiency was cold: 50.0% FG (-6.4% vs L10 avg of 56.4%). 2/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 11.3 pts — actual 12 was 0.7 pts close (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 12 pts vs 13.5 line (-1.5), UNDER hit by 1.5 pts. Suggs played 34 min (+3.4 vs L10 avg of 30.5) — 11% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 41.7%). Signals that called it correctly: Volume, HR L10, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L30, Trend, FG Trend. Projection model targeted 7.6 pts — actual 12 was 4.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Anthony Black</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Black scored 14 pts vs 8.5 line (+5.5), OVER hit by 5.5 pts. Black played 16 min (-13.3 vs L10 avg of 28.8) — 46% less than expected. Shooting was in line with averages: 36.4% FG (4/11, L10 avg 37.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.3 pts — actual 14 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Black's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 25 pts vs 19.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 32.8. Shooting efficiency was hot: 52.9% FG (+7.8% vs L10 avg of 45.1%). 9/17 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 21.4 pts — actual 25 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Reed scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 19 played vs L10 avg 18.2. Shooting efficiency was cold: 57.1% FG (-6.7% vs L10 avg of 63.8%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 6.2 pts — actual 9 was 2.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Reed's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 8 pts vs 10.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 28.3. Shooting efficiency was hot: 80.0% FG (+25.1% vs L10 avg of 54.9%). 4/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, FG Trend, Min Trend. Projection model targeted 8.2 pts — actual 8 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E23" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 17 pts vs 12.5 line (+4.5), UNDER missed by 4.5 pts. Huerter played 32 min (+6.9 vs L10 avg of 24.8) — 28% more than expected. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 45.9%). Counter-signals that proved correct: Trend, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.3 pts — actual 17 was 8.7 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Huerter's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jenkins scored 18 pts vs 19.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 34 played vs L10 avg 35.8. Shooting efficiency was hot: 54.5% FG (+9.3% vs L10 avg of 45.2%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 2.7 pts — actual 18 was 15.3 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jenkins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Carter scored 0 pts vs 6.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 19 played vs L10 avg 20.8. Shooting efficiency was cold: 0.0% FG (-39.6% vs L10 avg of 39.6%). 0/3 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.6 pts — actual 0 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Carter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Duren scored 18 pts vs 21.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 31.3. Shooting efficiency was hot: 77.8% FG (+11.1% vs L10 avg of 66.7%). 7/9 from the field. Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.3 pts — actual 18 was 2.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Duren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Coward scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Coward played 18 min (-7.9 vs L10 avg of 25.4) — 31% less than expected. Shooting efficiency was hot: 83.3% FG (+39.3% vs L10 avg of 44.0%). 5/6 from the field. Signals that called it correctly: Context, Defense, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.3 pts — actual 12 was 2.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Coward's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Merrill scored 21 pts vs 16.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 28 played vs L10 avg 28.7. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 40.6%). Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.9 pts — actual 21 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 11 pts vs 16.5 line (-5.5), UNDER hit by 5.5 pts. Jackson played 18 min (-8.4 vs L10 avg of 26.5) — 32% less than expected. Shooting efficiency was cold: 33.3% FG (-19.3% vs L10 avg of 52.6%). 3/9 from the field. Signals that called it correctly: HR L30, Context, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 5.0 pts — actual 11 was 6.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Keon Ellis</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ellis scored 19 pts vs 13.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 27 played vs L10 avg 26.2. Shooting efficiency was hot: 63.6% FG (+9.5% vs L10 avg of 54.1%). 7/11 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.7 pts — actual 19 was 13.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mobley scored 24 pts vs 21.5 line (+2.5), UNDER missed by 2.5 pts. Mobley played 26 min (-5.4 vs L10 avg of 31.1) — 17% less than expected. Shooting efficiency was hot: 81.8% FG (+18.0% vs L10 avg of 63.8%). 9/11 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.7 pts — actual 24 was 2.3 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mobley for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Schröder scored 22 pts vs 14.5 line (+7.5), UNDER missed by 7.5 pts. Schröder played 29 min (+10.4 vs L10 avg of 18.9) — 55% more than expected. Shooting efficiency was hot: 66.7% FG (+31.1% vs L10 avg of 35.6%). 8/12 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.8 pts — actual 22 was 13.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Allen scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 25 played vs L10 avg 26.7. Shooting was in line with averages: 71.4% FG (5/7, L10 avg 70.5%). Signals that called it correctly: Trend, H2H, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.4 pts — actual 13 was 1.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Allen in this role.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Prosper scored 24 pts vs 12.5 line (+11.5), UNDER missed by 11.5 pts. Prosper played 19 min (-4.4 vs L10 avg of 23.8) — 18% less than expected. Shooting efficiency was hot: 83.3% FG (+29.9% vs L10 avg of 53.4%). 10/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, FG Trend, Min Trend. Projection model targeted 10.8 pts — actual 24 was 13.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Prosper for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 5 pts vs 10.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 29 played vs L10 avg 29.0. Shooting efficiency was cold: 28.6% FG (-15.8% vs L10 avg of 44.4%). 2/7 from the field. Signals that called it correctly: Trend, Defense, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.7 pts — actual 5 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Castle scored 19 pts vs 17.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 31 played vs L10 avg 30.5. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 49.3%). Counter-signals that proved correct: HR L10, Trend, Defense, Min Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.8 pts — actual 19 was 3.2 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. Edgecombe played 41 min (+7.3 vs L10 avg of 33.5) — 22% more than expected. Shooting efficiency was cold: 40.0% FG (-11.5% vs L10 avg of 51.5%). 6/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 2.1 pts — actual 14 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 15 pts vs 24.5 line (-9.5), OVER missed by 9.5 pts. Minutes were as expected: 40 played vs L10 avg 37.1. Shooting efficiency was cold: 37.5% FG (-7.9% vs L10 avg of 45.4%). 6/16 from the field. Counter-signals that proved correct: Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 26.1 pts — actual 15 was 11.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Fox scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 26 played vs L10 avg 27.7. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 49.0%). Signals that called it correctly: HR L30, HR L10, Trend, Context, Pace (7/10 aligned). Counter-signals that were wrong: Volume, Defense, H2H. Projection model targeted 13.0 pts — actual 13 was 0.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Fox in this role.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 6 pts vs 5.5 line (+0.5), UNDER missed by 0.5 pts. Barlow played 16 min (-6.1 vs L10 avg of 22.1) — 28% less than expected. Shooting efficiency was hot: 66.7% FG (+8.4% vs L10 avg of 58.3%). 2/3 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 2.7 pts — actual 6 was 3.3 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barlow for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Wembanyama scored 17 pts vs 28.5 line (-11.5), UNDER hit by 11.5 pts. Wembanyama played 16 min (-14.3 vs L10 avg of 30.0) — 48% less than expected. Shooting efficiency was hot: 63.6% FG (+12.7% vs L10 avg of 50.9%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 18.7 pts — actual 17 was 1.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Wembanyama in this role.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 13 pts vs 12.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 25 played vs L10 avg 23.1. Shooting efficiency was cold: 28.6% FG (-22.0% vs L10 avg of 50.6%). 4/14 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.5 pts — actual 13 was 2.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 17 pts vs 11.5 line (+5.5), OVER hit by 5.5 pts. Harper played 28 min (+4.4 vs L10 avg of 23.5) — 19% more than expected. Shooting was in line with averages: 63.6% FG (7/11, L10 avg 59.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 19.9 pts — actual 17 was 2.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Harper's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 16 pts vs 17.5 line (-1.5), OVER missed by 1.5 pts. George played 38 min (+4.9 vs L10 avg of 33.2) — 15% more than expected. Shooting efficiency was cold: 33.3% FG (-13.5% vs L10 avg of 46.8%). 5/15 from the field. Counter-signals that proved correct: HR L30, Defense, H2H. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 17.9 pts — actual 16 was 1.9 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Champagnie scored 7 pts vs 10.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 27 played vs L10 avg 27.0. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 47.3%). Signals that called it correctly: Context, H2H, Pace (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.0 pts — actual 7 was 3.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Champagnie's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Vassell scored 9 pts vs 12.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 30 played vs L10 avg 30.0. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 42.7%). Counter-signals that proved correct: HR L30, HR L10, Trend, Pace. Signals that were wrong: Volume, Context, Defense. Projection model targeted 12.8 pts — actual 9 was 3.8 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Vassell's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Embiid scored 34 pts vs 27.5 line (+6.5), UNDER missed by 6.5 pts. Embiid played 39 min (+5.9 vs L10 avg of 33.2) — 18% more than expected. Shooting efficiency was cold: 42.1% FG (-7.8% vs L10 avg of 49.9%). 8/19 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, FG Trend. Projection model targeted 13.0 pts — actual 34 was 21.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gordon scored 23 pts vs 15.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 31 played vs L10 avg 28.7. Shooting efficiency was hot: 57.1% FG (+12.6% vs L10 avg of 44.5%). 8/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 11.0 pts — actual 23 was 12.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>WIN — III scored 6 pts vs 7.5 line (-1.5), UNDER hit by 1.5 pts. III played 23 min (+5.2 vs L10 avg of 17.8) — 29% more than expected. Shooting efficiency was cold: 50.0% FG (-10.1% vs L10 avg of 60.1%). 2/4 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, Pace, Min Trend. Projection model targeted 5.6 pts — actual 6 was 0.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for III in this role.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 30 pts vs 14.5 line (+15.5), UNDER missed by 15.5 pts. Camara played 35 min (+3.2 vs L10 avg of 31.7) — 10% more than expected. Shooting efficiency was hot: 62.5% FG (+7.2% vs L10 avg of 55.3%). 10/16 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.4 pts — actual 30 was 17.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 3 pts vs 11.5 line (-8.5), OVER missed by 8.5 pts. Minutes were as expected: 23 played vs L10 avg 23.7. Shooting efficiency was cold: 14.3% FG (-25.4% vs L10 avg of 39.7%). 1/7 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.8 pts — actual 3 was 11.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 18 pts vs 12.5 line (+5.5), OVER hit by 5.5 pts. Clingan played 30 min (+4.2 vs L10 avg of 25.8) — 16% more than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 50.0%). Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 16.9 pts — actual 18 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clingan in this role.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 6 pts vs 7.5 line (-1.5), OVER missed by 1.5 pts. Brown played 24 min (+3.5 vs L10 avg of 20.7) — 17% more than expected. Shooting efficiency was cold: 16.7% FG (-32.0% vs L10 avg of 48.7%). 1/6 from the field. Counter-signals that proved correct: HR L30, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 8.6 pts — actual 6 was 2.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Murray scored 20 pts vs 24.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 38 played vs L10 avg 37.4. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 50.2%). Counter-signals that proved correct: HR L30, HR L10, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 24.5 pts — actual 20 was 4.5 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Braun scored 8 pts vs 11.5 line (-3.5), OVER missed by 3.5 pts. Braun played 40 min (+8.8 vs L10 avg of 31.1) — 28% more than expected. Shooting was in line with averages: 57.1% FG (4/7, L10 avg 58.0%). Counter-signals that proved correct: HR L30, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 12.7 pts — actual 8 was 4.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Henderson scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. Henderson played 36 min (+11.6 vs L10 avg of 24.1) — 48% more than expected. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 43.4%). Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.7 pts — actual 18 was 6.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Henderson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 17 pts vs 12.5 line (+4.5), UNDER missed by 4.5 pts. Johnson played 37 min (+7.0 vs L10 avg of 29.7) — 24% more than expected. Shooting efficiency was hot: 66.7% FG (+14.8% vs L10 avg of 51.9%). 6/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Pace, Min Trend. Projection model targeted 11.6 pts — actual 17 was 5.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jokić scored 35 pts vs 27.5 line (+7.5), UNDER missed by 7.5 pts. Jokić played 43 min (+7.1 vs L10 avg of 36.1) — 20% more than expected. Shooting efficiency was cold: 48.4% FG (-8.3% vs L10 avg of 56.7%). 15/31 from the field. Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 23.8 pts — actual 35 was 11.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Avdija scored 26 pts vs 25.5 line (+0.5), UNDER missed by 0.5 pts. Avdija played 40 min (+7.7 vs L10 avg of 31.8) — 24% more than expected. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 43.5%). Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 23.7 pts — actual 26 was 2.3 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 19 pts vs 17.5 line (+1.5), UNDER missed by 1.5 pts. Holiday played 39 min (+9.0 vs L10 avg of 29.9) — 30% more than expected. Shooting efficiency was cold: 36.8% FG (-6.3% vs L10 avg of 43.1%). 7/19 from the field. Counter-signals that proved correct: HR L30, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 15.6 pts — actual 19 was 3.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:51</t>
+        </is>
       </c>
     </row>
   </sheetData>
